--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614BA877-6CD5-412E-A68B-8EB8B7B9A894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F5B7DC-CD7D-4632-9FD4-492B87C5EAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31185" yWindow="7305" windowWidth="20340" windowHeight="13005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,9 +79,6 @@
     <t>Artificial Intelligence</t>
   </si>
   <si>
-    <t>artificial;intelligence</t>
-  </si>
-  <si>
     <t>Revolutionise</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
   </si>
   <si>
     <t>debate</t>
+  </si>
+  <si>
+    <t>artificial//intelligence</t>
   </si>
 </sst>
 </file>
@@ -561,7 +561,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -569,13 +569,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -583,13 +583,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -597,13 +597,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -611,13 +611,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -625,13 +625,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -639,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -653,13 +653,13 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F5B7DC-CD7D-4632-9FD4-492B87C5EAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA832F11-4B53-4A55-9942-A978CA3AEF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31185" yWindow="7305" windowWidth="20340" windowHeight="13005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14004" yWindow="4428" windowWidth="21600" windowHeight="15924" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="167">
   <si>
     <t>type</t>
   </si>
@@ -43,9 +43,6 @@
     <t>How Artificial Intelligence Can Revolutionise Science</t>
   </si>
   <si>
-    <t>人工智能如何能够给科学带来革命性的改变</t>
-  </si>
-  <si>
     <t>word</t>
   </si>
   <si>
@@ -58,18 +55,12 @@
     <t>Debate about artificial intelligence tends to focus on its potential dangers:</t>
   </si>
   <si>
-    <t>有关人工智能的辩论通常倾向于聚焦在它的潜在危害上</t>
-  </si>
-  <si>
     <t>paragrah</t>
   </si>
   <si>
     <t>algorithmic bias and discrimination, the mass destruction of jobs and even, some say, the extinction of humanity.</t>
   </si>
   <si>
-    <t>算法偏见与歧视、大规模摧毁岗位，甚至还有一些人提到的人类灭亡</t>
-  </si>
-  <si>
     <t>isPhrase</t>
   </si>
   <si>
@@ -107,25 +98,586 @@
   </si>
   <si>
     <t>artificial//intelligence</t>
+  </si>
+  <si>
+    <t>As some observers fret about these dystopian scewnarios, however, others are focusing on potential rewards.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI could, they claim, help humanity solve some of its biggest and thorniest problems.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bias</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>humanity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>observer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fret</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>observers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dystopian</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorniest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>And, they say, AI will do this in a very specific way:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>by radically accelerating the pace of scientific discovery, especially in areas such as medicine, climate science and green technology.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>radically</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorny</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>accelerating</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>accelerate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>medicine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luminaries in the field such as Demis Hassabis and Yann LeCun believe that AI can turbocharge scientific progress and lead to a golden age of discovery.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Could they be right?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luminaries</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>luminary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>turbocharge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能如何能够给科学带来革命性的改变。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有关人工智能的辩论通常倾向于聚焦在它的潜在危害上。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>算法偏见与歧视、大规模摧毁岗位，甚至还有一些人提到的人类灭亡。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过，在一些评论家位这些反乌托邦情境烦恼的同时，其他人关注的则是其潜在的回报。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>他们称人工智能可以帮助人类解决一些最大、最棘手的问题。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>他们还说，人工智能将以一种非常独特的方式做到这一点：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大幅加快科学发现的步伐，尤其是在医学、气候科学以及绿色技术等领域。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>领域内的杰出人物-诸如德米耶·哈萨比斯以及扬·莱坎（杨立昆）等-都认为，人工智能可以大大推动科研进展，并开启科学发现的黄金时代，</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>他们会是正确的吗？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Such claims are worth examining, and may provide a useful counterbalance to fears about large-scale unemployment and killer robots.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterbalance</t>
+  </si>
+  <si>
+    <t>Many previous technologies have, of course, been falsely hailed as panaceas.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hailed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hail</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>panaceas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>panacea</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The electric telegraph was lauded in the 1850s as a herald of world peace, as were aircraft in the 1900s;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pundits in the 1990s said the internet would reduce inequality and eradicate nationalism.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>telegraph</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lauded</t>
+  </si>
+  <si>
+    <t>laud</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>herald</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pundits</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pundit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eradicate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nationalism</t>
+  </si>
+  <si>
+    <t>But the mechanism by which AI will supposedly solve the world's problems has a stronger historical basis, because there have been several periods in the history when new approaches and new tools did indeed help bring about bursts of world-changing sciectific discovery and innovation.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>supposedly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>approaches</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>approache</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bring about</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bring</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bursts</t>
+  </si>
+  <si>
+    <t>burst</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这类说法值得思考，并且或许能提供一种有用的论点来调节对大规模失业和杀手机器人的恐惧。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，以前有许多技术曾被错误地称颂为灵丹妙药。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>电报技术曾在19世纪50年代被称赞为世界和平的使者，飞机在20世纪头十年也受到同样的赞誉；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20世纪90年代，专家曾说，互联网将减少不平等，消除民族主义。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是，人们认为人工智能能够用来解决世界问题的机制有着更强的历史基础，因为在历史上的多个阶段，新方法与新工具都的确带来了足以改变世界的科学发现与创新的迸发。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>In the 17th century microscopes and telescopes opened up new vistas of discovery and encouraged researchers to favour their own obsercations over the received wisdom of antiquity, while the introduction of scientific jourals gave them new ways to share and publicise their finding.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>microscopes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>microscope</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>telescopes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>telescope</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vistas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vista</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>received wisdom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>received//widom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>antiquity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>publicise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The result was rapid progress in astronomy, physics and other fields, and new inventions from the pendulum clock to the steam engine-the prime mover of the Industrial Revolition.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>astronomy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pendulum</t>
+  </si>
+  <si>
+    <t>prime mover</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>prime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>the Industrial Revolition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrial//revolition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在17世纪，显微镜与望远镜开启了科学发现的新前景，鼓励研究者坚持自己的观察结果，而不是公认的古人智慧，与此同时，科学学术期刊的出现给予他们分享与公开自己发现的新途径。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>由此，天文学、物理学和其他领域得以快速发展，新发明不断涌现，例如摆钟以及蒸汽机，后者是工业革命的主要驱动力。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Then, starting in the late 19th century, the establishment of research laboratories, which brought together ideas, people and materials on an industrial scale, gave rise to further innovations such as artificial fertiliser, pharmaceuticals and the transistor, the building block of the computer.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>establishment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>scale</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>on a * scale</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>give</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fertiliser</t>
+  </si>
+  <si>
+    <t>pharmaceuticals</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pharmaceutical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>transistor</t>
+  </si>
+  <si>
+    <t>building block</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>building</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>From the mid-20th century, computers in turn enabled new forms of science based on simulation and modelling, from the design of weapons and aircraft to more accurate weather forecasting.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>simulation</t>
+  </si>
+  <si>
+    <t>simulation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>modelling</t>
+  </si>
+  <si>
+    <t>accurate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>随后，从19世纪末开始，研究实验室的建立使思想、人员和材料能够以工业规模聚焦，催生了更多的创新成果，例如化肥、药品以及计算机的构件晶体管。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从20世纪中叶开始，计算机反过来使得模拟与建模的新型科学成为可能，从武器与飞机的设计到更精确的气象预测等不一而足。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>And the computer revolution may not be finished yet.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As we report in a special Science section, AI tools and techniques are now being applies in almost every field of science, though the degree of adoption varies sidely:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.2% of physics and astronomy papers published in 2022 involved AI, for example, compared with 1.4% in veterinary science.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>adoption</t>
+  </si>
+  <si>
+    <t>involved</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>involve</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>veterinary</t>
+  </si>
+  <si>
+    <t>gave rise to</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI is being employed in many ways.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It can identify promising candidates for anlysis, such as molecules with particular properities in drug discovery, or materials with the characteristics needed in batteries or solar cells.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>promising</t>
+  </si>
+  <si>
+    <t>candidates</t>
+  </si>
+  <si>
+    <t>candidate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>molecules</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>molecule</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>properities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>properity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>solar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>solar cell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>而且，计算机革命可能尚未完结。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正如我们在科学特别板块里报道的那样，人工智能工具与技术如今正被应用于几乎每一个科学领域，尽管各领域的应用程度大有不同：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>例如在2022年，物理学和天文学方面发表的论文中有7.2%与人工智能相关，而兽医学中这一比例只有1.4%。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能的应用方式也很多。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它可以识别有前景的分析样本，例如在药物研究中拥有特定属性的分子，或者拥有电池或太阳能电池所需特性的材料。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>It can sift through piles of data such as those produced bu particle colliders or robotic telescopes, looking for patterns.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>And AI can model and analyse even more complex systems, such as the folding of proteins and the formation of galaxies.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI tools have been used to identify new antibiotics, reveal the Higgs boson and spot regional accents in wolves, among other things.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sift through</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sift</t>
+  </si>
+  <si>
+    <t>particle</t>
+  </si>
+  <si>
+    <t>colliders</t>
+  </si>
+  <si>
+    <t>collider</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>patterns</t>
+  </si>
+  <si>
+    <t>pattern</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>the folding of proteins</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>protein</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>galaxies</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>galaxy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>among other things</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>among</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>antibiotics</t>
+  </si>
+  <si>
+    <t>antibiotic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它可以筛选大量数据以寻找规律，例如由粒子对撞机或者远程望远镜产生的数据。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能还可以建模并分析更加复杂的系统，例如蛋白质的折叠以及星系的形成等。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能工具还已被用于辨识新的抗生素、揭秘希格斯玻色子，以及发现狼的地方口音等。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -166,7 +718,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -444,24 +996,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="78.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -484,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -492,177 +1044,1437 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C86412D-EF50-4A2E-8A10-147D1E09B5C3}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3</v>
       </c>
       <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24">
         <v>24</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>17</v>
+      </c>
+      <c r="B45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>17</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>17</v>
+      </c>
+      <c r="B49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>17</v>
+      </c>
+      <c r="B50" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>18</v>
+      </c>
+      <c r="B51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>18</v>
+      </c>
+      <c r="B52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>18</v>
+      </c>
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>20</v>
+      </c>
+      <c r="B54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>21</v>
+      </c>
+      <c r="B56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>23</v>
+      </c>
+      <c r="B57" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>23</v>
+      </c>
+      <c r="B58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>23</v>
+      </c>
+      <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" t="s">
+        <v>136</v>
+      </c>
+      <c r="E59">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>23</v>
+      </c>
+      <c r="B60" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>23</v>
+      </c>
+      <c r="B61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>139</v>
+      </c>
+      <c r="E61">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>24</v>
       </c>
+      <c r="B62" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>150</v>
+      </c>
+      <c r="E62">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>24</v>
+      </c>
+      <c r="B63" t="s">
+        <v>151</v>
+      </c>
+      <c r="D63" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>24</v>
+      </c>
+      <c r="B64" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>24</v>
+      </c>
+      <c r="B65" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" t="s">
+        <v>155</v>
+      </c>
+      <c r="E65">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>157</v>
+      </c>
+      <c r="E66">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>158</v>
+      </c>
+      <c r="D67" t="s">
+        <v>159</v>
+      </c>
+      <c r="E67">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>26</v>
+      </c>
+      <c r="B68" t="s">
+        <v>162</v>
+      </c>
+      <c r="D68" t="s">
+        <v>163</v>
+      </c>
+      <c r="E68">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>26</v>
+      </c>
+      <c r="B69" t="s">
+        <v>160</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>161</v>
+      </c>
+      <c r="E69">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1089E9-9F35-467C-BD20-C80F3A77E7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26487102-FC04-451A-9C35-303131B914E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31740" yWindow="6180" windowWidth="28500" windowHeight="13005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32820" yWindow="7035" windowWidth="28500" windowHeight="13005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="186">
   <si>
     <t>type</t>
   </si>
@@ -679,6 +679,18 @@
   </si>
   <si>
     <t>characteristic</t>
+  </si>
+  <si>
+    <t>pace</t>
+  </si>
+  <si>
+    <t>especially</t>
+  </si>
+  <si>
+    <t>climate</t>
+  </si>
+  <si>
+    <t>scientific</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C86412D-EF50-4A2E-8A10-147D1E09B5C3}">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.85546875" customWidth="1"/>
@@ -1811,296 +1823,281 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23">
-        <v>15</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24">
-        <v>16</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>10</v>
-      </c>
-      <c r="B26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" t="s">
-        <v>159</v>
+        <v>7</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30">
-        <v>24</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F33">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F34">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F35">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F36">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="F37">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F38">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F39">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F40">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="F41">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>73</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F42">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="F43">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2108,13 +2105,13 @@
         <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F44">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2122,143 +2119,134 @@
         <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F45">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F46">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>177</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="F47">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="F48">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="F49">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F50">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>173</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D51" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" t="s">
-        <v>171</v>
+        <v>92</v>
       </c>
       <c r="F51">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
-      </c>
-      <c r="E52" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F52">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>161</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="F53">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2266,13 +2254,13 @@
         <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F54">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2280,13 +2268,19 @@
         <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>173</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
+        <v>96</v>
+      </c>
+      <c r="E55" t="s">
+        <v>171</v>
       </c>
       <c r="F55">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2294,156 +2288,162 @@
         <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>97</v>
+      </c>
+      <c r="E56" t="s">
+        <v>175</v>
       </c>
       <c r="F56">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F57">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F58">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F59">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>169</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F60">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D61" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F61">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F62">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F63">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D64" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F64">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F65">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="F66">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2451,10 +2451,13 @@
         <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>119</v>
       </c>
       <c r="D67" t="s">
-        <v>181</v>
+        <v>119</v>
+      </c>
+      <c r="F67">
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2462,136 +2465,189 @@
         <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F68">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F69">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="F70">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
-      </c>
-      <c r="F71">
-        <v>65</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>168</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F72">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F73">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F74">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F75">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
+        <v>24</v>
+      </c>
+      <c r="B76" t="s">
+        <v>138</v>
+      </c>
+      <c r="D76" t="s">
+        <v>139</v>
+      </c>
+      <c r="F76">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>167</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>141</v>
+      </c>
+      <c r="D78" t="s">
+        <v>142</v>
+      </c>
+      <c r="F78">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
         <v>26</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B79" t="s">
+        <v>144</v>
+      </c>
+      <c r="D79" t="s">
+        <v>145</v>
+      </c>
+      <c r="F79">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s">
         <v>166</v>
       </c>
-      <c r="C76">
+      <c r="C80">
         <v>1</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D80" t="s">
         <v>143</v>
       </c>
-      <c r="F76">
+      <c r="F80">
         <v>71</v>
       </c>
     </row>

--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26487102-FC04-451A-9C35-303131B914E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEA40CE-8CCA-4895-ADAC-69C6B0FFA617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32820" yWindow="7035" windowWidth="28500" windowHeight="13005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5640" yWindow="8016" windowWidth="21600" windowHeight="15936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
     <sheet name="01_words" sheetId="2" r:id="rId2"/>
+    <sheet name="02_contents" sheetId="3" r:id="rId3"/>
+    <sheet name="02_words" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="299">
   <si>
     <t>type</t>
   </si>
@@ -691,30 +693,472 @@
   </si>
   <si>
     <t>scientific</t>
+  </si>
+  <si>
+    <t>All this is to be welcomed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>But the journal and the laboratory went further still:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>they altered scientific practice itself and unlocked more powerful means of making discoveries, by allowing people and ideas to mingle in new ways and on a larger scale.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI, too, has the potential to set off such a transformation.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mingle</t>
+  </si>
+  <si>
+    <t>set off</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>set</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些都是喜人的成果。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但学术期刊和实验室产生的影响可不止于此：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们使人员与思想能够以新的方式和更大的规模实现融合，从而改变了科学实践本身，解锁了更多能够取得发现的强大工具。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能同样也有引发这种转变的潜力。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two areas in particular look promising.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The first is "literature-based discovery"(LBD), which involves analysing existing scientific literature, using ChatGPT-style language analysis, to look for new hypotheses, connections or ideas that humans may have missed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD us showing promise un udentufyung new experiments to try - and even suggesting potential research collaborators.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This could stimulate interdisciplinary work and foster innovation at the boundaries between fields.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD systems can also identify "blind spots" in given field, and even predict future discoveries and who will make them.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>literature</t>
+  </si>
+  <si>
+    <t>hypotheses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypothesis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>suggesting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>suggest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stimulate</t>
+  </si>
+  <si>
+    <t>interdisciplinary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>foster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>boundaries</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>boundary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fields</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>field</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blind spots</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blind spot</t>
+  </si>
+  <si>
+    <t>blind//spot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The second area is "robot scientists", also known as "self-driving labs".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>These are robotic systems that use AI to from new hypotheses, based on anlysis of existing data and literature, and then test those hypotheses bu performing hundreds or thousands of experiments, in fileds incliding systems biology and materials science.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlike human scientists, robots are less attached to previous results, less driven by bias - and, crucially, easy to replicate.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>They could scale up experimental research, develop unexpected theories and explore avenues that human investigators might not have considered.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>systems biology</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>biology</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>attached</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>replicate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>scale up</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>avenues</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>avenue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有两个领域看起来尤为有前景。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先是“基于文献的发现”（LBD），这包含分析现有科学文献，使用类似ChatGPT的语言分析方式来寻找人们可能未察觉到的新假设、新联系或者新想法。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD在确定可尝试的新实验方面正展现出潜力-它甚至能够推荐潜在的研究合作者。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这有可能促进跨学科研究，并在不同学科的交叉领域培育创新。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD系统还可以识别特定领域的“盲点”，甚至预测未来的发现以及发现者。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二个领域是“机器人科学家”，它们也被称为“自驱型实验室”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些机器人系统以对现有数据和文献的分析为基础，使用人工智能来形成新的假设，然后通过开展数百数千次实验来验证这些假设，涉及领域包括系统生物学和材料科学等。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>与人类科学家不同，机器人受以往研究结果的牵绊更少，受偏见的影响也要更小-关键是其容易复制。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们可以扩大实验性研究的规模，发展出意想不到的理论，并探索人类研究者或许从未思考过的道路。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The idea that AI might transform scientific practice is therefore feasible.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>But the main barrier is sociological:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>it can happen only if human scientists are willing and able to use such tools.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Many lack skills and training;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>some worry about being put out of a job.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fortunately, there are hopeful signs.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI tools are now moving from being pushed by AI researchers to being embraced by specialists in other fields.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>feasible</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sociological</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>embraced</t>
+  </si>
+  <si>
+    <t>embrace</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，人工智能或许会给科学实践带来变革的想法是可行的。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但主要障碍来自社会：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有在人类科学家愿意并有能力运用这类工具时，它才有可能发生。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>许多人类科学家缺少技能与训练；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有些人担心失业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸运的是，还是有一些乐观的迹象。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能工具如今正在从由人工智能研究者大力推动转变为受到其他领域专家热烈欢迎。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Governments and funding bodies could help by pressing for greater use of common strandards to allow AI systems to exchange and interpret laboratory results and other data.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thet could also fund more research into the integration of AI smarts with laboratory robotics, and into forms of AI beyond those being pursued in the private sector, which has bet nearly all its chips on language-based systems like ChatGPT.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less fashionable forms of AI, such as, model-based machine learning, may be better suited to scientific tasks such as forming hypotheses.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bodies</t>
+  </si>
+  <si>
+    <t>body</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pressing for</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>press</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>press for sth.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>integration</t>
+  </si>
+  <si>
+    <t>integration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>smarts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>robotics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chip</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The adding of the artificial</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>政府与融资机构也能帮上忙，例如大力敦促更多地使用共同标准，使人工智能得以用来交流并解读实验室结果和其他数据。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们还可以资助更多研究，从而促进人工智能的智力与实验室机器人技术相融合，以及研究那些未受私营部门追捧的人工智能类型。私营部门几乎将所有筹码都押注在了ChatGPT这类以语言为基础的人工智能系统之上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不那么流行的人工智能类型，例如以模型为基础的机器学习，或许更适合像提出假设这样的科学任务。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工造物的添加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 1655, during a period of repid scientific progress, Robert Hooke, an English polymath, described the advent of new scientific instruments such as the microscope and telescope as "the adding of artificial organs to the natural".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>They let researchers explore previously inaccessible realms and discover things in new ways, "with prodigious benefit to all sorts of useful knowledge".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For Hooke's modern-day successors, the adding of artificial intelligence to the scientific toolkit is poised to do the same in the coming years - with similarly world-changing results.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>polymath</t>
+  </si>
+  <si>
+    <t>advent</t>
+  </si>
+  <si>
+    <t>organs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>organ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>inaccessible</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>realms</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>realm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>prodigious</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>successors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>successor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>toolkit</t>
+  </si>
+  <si>
+    <t>poised</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>poise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1655年，在那段科学快速发展的时期，英国博学家罗伯特·胡克曾将显微镜与望远镜这类新型科学工具的出现描述为“为人体添加人工器官”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们让研究者得以探索此前无法触及的领域，并以新的方式发现事物，“给所有类型的有用知识都带来了巨大好处”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对胡克的现代后继者而言，在科学工具箱中添加人工智能也有望在未来几年产生同样的效果-也将取得类似的改变世界的成果。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI And Culture: The Dawn Of The Omnistar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能与文化：全能明星将至</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dawn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dawn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Omnistar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>omnistar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -760,7 +1204,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1038,16 +1482,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1064,7 +1508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1081,7 +1525,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1098,7 +1542,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30">
+    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1115,7 +1559,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1132,7 +1576,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1149,7 +1593,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1166,7 +1610,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1183,7 +1627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1200,7 +1644,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1217,7 +1661,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1234,7 +1678,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1251,7 +1695,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1268,7 +1712,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1285,7 +1729,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="60">
+    <row r="15" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1302,7 +1746,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="60">
+    <row r="16" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1319,7 +1763,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="45">
+    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1336,7 +1780,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="60">
+    <row r="18" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1353,7 +1797,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="45">
+    <row r="19" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1370,7 +1814,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1387,7 +1831,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="30">
+    <row r="21" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1404,7 +1848,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="30">
+    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1421,7 +1865,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1438,7 +1882,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="45">
+    <row r="24" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1455,7 +1899,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="30">
+    <row r="25" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1472,7 +1916,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="30">
+    <row r="26" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1489,7 +1933,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="30">
+    <row r="27" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1504,6 +1948,465 @@
       </c>
       <c r="E27" s="3" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>8</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>9</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>9</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>9</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>10</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>11</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>12</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>12</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -1514,17 +2417,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C86412D-EF50-4A2E-8A10-147D1E09B5C3}">
-  <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F114"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1541,7 +2444,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1558,7 +2461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1572,7 +2475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1583,7 +2486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1594,7 +2497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1605,7 +2508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1619,7 +2522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1630,7 +2533,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1644,7 +2547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1658,7 +2561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1672,7 +2575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1686,7 +2589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1700,7 +2603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4</v>
       </c>
@@ -1717,7 +2620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1731,7 +2634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>4</v>
       </c>
@@ -1742,7 +2645,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4</v>
       </c>
@@ -1753,7 +2656,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -1764,7 +2667,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -1778,7 +2681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>6</v>
       </c>
@@ -1790,7 +2693,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7</v>
       </c>
@@ -1804,7 +2707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
@@ -1818,7 +2721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -1829,7 +2732,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7</v>
       </c>
@@ -1840,7 +2743,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>7</v>
       </c>
@@ -1854,7 +2757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>7</v>
       </c>
@@ -1865,7 +2768,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>8</v>
       </c>
@@ -1879,7 +2782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>8</v>
       </c>
@@ -1893,7 +2796,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>8</v>
       </c>
@@ -1904,7 +2807,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>10</v>
       </c>
@@ -1915,7 +2818,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>10</v>
       </c>
@@ -1929,7 +2832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>11</v>
       </c>
@@ -1943,7 +2846,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>11</v>
       </c>
@@ -1957,7 +2860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>12</v>
       </c>
@@ -1971,7 +2874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>12</v>
       </c>
@@ -1985,7 +2888,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>12</v>
       </c>
@@ -1999,7 +2902,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>13</v>
       </c>
@@ -2013,7 +2916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>13</v>
       </c>
@@ -2027,7 +2930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>13</v>
       </c>
@@ -2041,7 +2944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>14</v>
       </c>
@@ -2055,7 +2958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>14</v>
       </c>
@@ -2069,7 +2972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>14</v>
       </c>
@@ -2086,7 +2989,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>14</v>
       </c>
@@ -2100,7 +3003,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>15</v>
       </c>
@@ -2114,7 +3017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>15</v>
       </c>
@@ -2128,7 +3031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>15</v>
       </c>
@@ -2142,7 +3045,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>15</v>
       </c>
@@ -2159,7 +3062,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>15</v>
       </c>
@@ -2173,7 +3076,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>15</v>
       </c>
@@ -2187,7 +3090,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>16</v>
       </c>
@@ -2201,7 +3104,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>16</v>
       </c>
@@ -2215,7 +3118,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>16</v>
       </c>
@@ -2232,7 +3135,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>16</v>
       </c>
@@ -2249,7 +3152,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>17</v>
       </c>
@@ -2263,7 +3166,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>17</v>
       </c>
@@ -2283,7 +3186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>17</v>
       </c>
@@ -2303,7 +3206,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>17</v>
       </c>
@@ -2317,7 +3220,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>17</v>
       </c>
@@ -2331,7 +3234,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>17</v>
       </c>
@@ -2345,7 +3248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>17</v>
       </c>
@@ -2362,7 +3265,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>18</v>
       </c>
@@ -2376,7 +3279,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>18</v>
       </c>
@@ -2390,7 +3293,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>18</v>
       </c>
@@ -2404,7 +3307,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>20</v>
       </c>
@@ -2418,7 +3321,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>21</v>
       </c>
@@ -2432,7 +3335,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>21</v>
       </c>
@@ -2446,7 +3349,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>23</v>
       </c>
@@ -2460,7 +3363,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>23</v>
       </c>
@@ -2474,7 +3377,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>23</v>
       </c>
@@ -2488,7 +3391,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>23</v>
       </c>
@@ -2502,7 +3405,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>23</v>
       </c>
@@ -2513,7 +3416,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>23</v>
       </c>
@@ -2530,7 +3433,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>24</v>
       </c>
@@ -2547,7 +3450,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>24</v>
       </c>
@@ -2561,7 +3464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>24</v>
       </c>
@@ -2575,7 +3478,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>24</v>
       </c>
@@ -2589,7 +3492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>25</v>
       </c>
@@ -2606,7 +3509,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>25</v>
       </c>
@@ -2620,7 +3523,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>26</v>
       </c>
@@ -2634,7 +3537,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>26</v>
       </c>
@@ -2649,6 +3552,503 @@
       </c>
       <c r="F80">
         <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>29</v>
+      </c>
+      <c r="B81" t="s">
+        <v>190</v>
+      </c>
+      <c r="D81" t="s">
+        <v>190</v>
+      </c>
+      <c r="F81">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>191</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>192</v>
+      </c>
+      <c r="F82">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>32</v>
+      </c>
+      <c r="B83" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" t="s">
+        <v>202</v>
+      </c>
+      <c r="F83">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>32</v>
+      </c>
+      <c r="B84" t="s">
+        <v>203</v>
+      </c>
+      <c r="D84" t="s">
+        <v>204</v>
+      </c>
+      <c r="F84">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>33</v>
+      </c>
+      <c r="B85" t="s">
+        <v>205</v>
+      </c>
+      <c r="D85" t="s">
+        <v>206</v>
+      </c>
+      <c r="F85">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>34</v>
+      </c>
+      <c r="B86" t="s">
+        <v>207</v>
+      </c>
+      <c r="D86" t="s">
+        <v>207</v>
+      </c>
+      <c r="F86">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>34</v>
+      </c>
+      <c r="B87" t="s">
+        <v>208</v>
+      </c>
+      <c r="D87" t="s">
+        <v>208</v>
+      </c>
+      <c r="F87">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>34</v>
+      </c>
+      <c r="B88" t="s">
+        <v>209</v>
+      </c>
+      <c r="D88" t="s">
+        <v>209</v>
+      </c>
+      <c r="F88">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>34</v>
+      </c>
+      <c r="B89" t="s">
+        <v>210</v>
+      </c>
+      <c r="D89" t="s">
+        <v>211</v>
+      </c>
+      <c r="F89">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>34</v>
+      </c>
+      <c r="B90" t="s">
+        <v>212</v>
+      </c>
+      <c r="D90" t="s">
+        <v>213</v>
+      </c>
+      <c r="F90">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>35</v>
+      </c>
+      <c r="B91" t="s">
+        <v>214</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91" t="s">
+        <v>216</v>
+      </c>
+      <c r="E91" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>37</v>
+      </c>
+      <c r="B92" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>38</v>
+      </c>
+      <c r="B93" t="s">
+        <v>223</v>
+      </c>
+      <c r="D93" t="s">
+        <v>223</v>
+      </c>
+      <c r="F93">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>38</v>
+      </c>
+      <c r="B94" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" t="s">
+        <v>224</v>
+      </c>
+      <c r="F94">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>39</v>
+      </c>
+      <c r="B95" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>96</v>
+      </c>
+      <c r="F95">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>39</v>
+      </c>
+      <c r="B96" t="s">
+        <v>226</v>
+      </c>
+      <c r="D96" t="s">
+        <v>227</v>
+      </c>
+      <c r="F96">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s">
+        <v>244</v>
+      </c>
+      <c r="D97" t="s">
+        <v>244</v>
+      </c>
+      <c r="F97">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>41</v>
+      </c>
+      <c r="B98" t="s">
+        <v>245</v>
+      </c>
+      <c r="D98" t="s">
+        <v>245</v>
+      </c>
+      <c r="F98">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>46</v>
+      </c>
+      <c r="B99" t="s">
+        <v>246</v>
+      </c>
+      <c r="D99" t="s">
+        <v>247</v>
+      </c>
+      <c r="F99">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>47</v>
+      </c>
+      <c r="B100" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" t="s">
+        <v>259</v>
+      </c>
+      <c r="F100">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>47</v>
+      </c>
+      <c r="B101" t="s">
+        <v>260</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
+        <v>261</v>
+      </c>
+      <c r="E101" t="s">
+        <v>262</v>
+      </c>
+      <c r="F101">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>48</v>
+      </c>
+      <c r="B102" t="s">
+        <v>264</v>
+      </c>
+      <c r="D102" t="s">
+        <v>263</v>
+      </c>
+      <c r="F102">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>48</v>
+      </c>
+      <c r="B103" t="s">
+        <v>265</v>
+      </c>
+      <c r="D103" t="s">
+        <v>265</v>
+      </c>
+      <c r="F103">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>48</v>
+      </c>
+      <c r="B104" t="s">
+        <v>266</v>
+      </c>
+      <c r="D104" t="s">
+        <v>266</v>
+      </c>
+      <c r="F104">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>48</v>
+      </c>
+      <c r="B105" t="s">
+        <v>267</v>
+      </c>
+      <c r="D105" t="s">
+        <v>268</v>
+      </c>
+      <c r="F105">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>51</v>
+      </c>
+      <c r="B106" t="s">
+        <v>277</v>
+      </c>
+      <c r="D106" t="s">
+        <v>277</v>
+      </c>
+      <c r="F106">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>51</v>
+      </c>
+      <c r="B107" t="s">
+        <v>278</v>
+      </c>
+      <c r="D107" t="s">
+        <v>278</v>
+      </c>
+      <c r="F107">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>51</v>
+      </c>
+      <c r="B108" t="s">
+        <v>279</v>
+      </c>
+      <c r="D108" t="s">
+        <v>280</v>
+      </c>
+      <c r="F108">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>52</v>
+      </c>
+      <c r="B109" t="s">
+        <v>281</v>
+      </c>
+      <c r="D109" t="s">
+        <v>281</v>
+      </c>
+      <c r="F109">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>52</v>
+      </c>
+      <c r="B110" t="s">
+        <v>282</v>
+      </c>
+      <c r="D110" t="s">
+        <v>283</v>
+      </c>
+      <c r="F110">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>52</v>
+      </c>
+      <c r="B111" t="s">
+        <v>284</v>
+      </c>
+      <c r="D111" t="s">
+        <v>284</v>
+      </c>
+      <c r="F111">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>53</v>
+      </c>
+      <c r="B112" t="s">
+        <v>285</v>
+      </c>
+      <c r="D112" t="s">
+        <v>286</v>
+      </c>
+      <c r="F112">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>53</v>
+      </c>
+      <c r="B113" t="s">
+        <v>287</v>
+      </c>
+      <c r="D113" t="s">
+        <v>287</v>
+      </c>
+      <c r="F113">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>53</v>
+      </c>
+      <c r="B114" t="s">
+        <v>288</v>
+      </c>
+      <c r="D114" t="s">
+        <v>289</v>
+      </c>
+      <c r="F114">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2656,4 +4056,124 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB71F98-C214-4E2A-8F31-34FC50527B4A}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F015AC71-3C0E-4B3C-9B3E-599310938E5F}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEA40CE-8CCA-4895-ADAC-69C6B0FFA617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9593C8-AEA9-4319-B193-20DB4720E1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="8016" windowWidth="21600" windowHeight="15936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50415" yWindow="5430" windowWidth="12360" windowHeight="14160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="308">
   <si>
     <t>type</t>
   </si>
@@ -330,10 +330,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>In the 17th century microscopes and telescopes opened up new vistas of discovery and encouraged researchers to favour their own obsercations over the received wisdom of antiquity, while the introduction of scientific jourals gave them new ways to share and publicise their finding.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>microscopes</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -714,453 +710,487 @@
     <t>mingle</t>
   </si>
   <si>
+    <t>set</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些都是喜人的成果。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但学术期刊和实验室产生的影响可不止于此：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们使人员与思想能够以新的方式和更大的规模实现融合，从而改变了科学实践本身，解锁了更多能够取得发现的强大工具。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能同样也有引发这种转变的潜力。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Two areas in particular look promising.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The first is "literature-based discovery"(LBD), which involves analysing existing scientific literature, using ChatGPT-style language analysis, to look for new hypotheses, connections or ideas that humans may have missed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD us showing promise un udentufyung new experiments to try - and even suggesting potential research collaborators.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This could stimulate interdisciplinary work and foster innovation at the boundaries between fields.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD systems can also identify "blind spots" in given field, and even predict future discoveries and who will make them.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>literature</t>
+  </si>
+  <si>
+    <t>hypotheses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hypothesis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>suggesting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>suggest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stimulate</t>
+  </si>
+  <si>
+    <t>interdisciplinary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>foster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>boundaries</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>boundary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fields</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>field</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blind spots</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blind spot</t>
+  </si>
+  <si>
+    <t>blind//spot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The second area is "robot scientists", also known as "self-driving labs".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>These are robotic systems that use AI to from new hypotheses, based on anlysis of existing data and literature, and then test those hypotheses bu performing hundreds or thousands of experiments, in fileds incliding systems biology and materials science.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlike human scientists, robots are less attached to previous results, less driven by bias - and, crucially, easy to replicate.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>They could scale up experimental research, develop unexpected theories and explore avenues that human investigators might not have considered.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>biology</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>attached</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>replicate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>scale up</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>avenues</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>avenue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有两个领域看起来尤为有前景。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先是“基于文献的发现”（LBD），这包含分析现有科学文献，使用类似ChatGPT的语言分析方式来寻找人们可能未察觉到的新假设、新联系或者新想法。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD在确定可尝试的新实验方面正展现出潜力-它甚至能够推荐潜在的研究合作者。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这有可能促进跨学科研究，并在不同学科的交叉领域培育创新。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LBD系统还可以识别特定领域的“盲点”，甚至预测未来的发现以及发现者。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二个领域是“机器人科学家”，它们也被称为“自驱型实验室”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这些机器人系统以对现有数据和文献的分析为基础，使用人工智能来形成新的假设，然后通过开展数百数千次实验来验证这些假设，涉及领域包括系统生物学和材料科学等。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>与人类科学家不同，机器人受以往研究结果的牵绊更少，受偏见的影响也要更小-关键是其容易复制。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们可以扩大实验性研究的规模，发展出意想不到的理论，并探索人类研究者或许从未思考过的道路。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The idea that AI might transform scientific practice is therefore feasible.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>But the main barrier is sociological:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>it can happen only if human scientists are willing and able to use such tools.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Many lack skills and training;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>some worry about being put out of a job.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fortunately, there are hopeful signs.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI tools are now moving from being pushed by AI researchers to being embraced by specialists in other fields.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>feasible</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sociological</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>embraced</t>
+  </si>
+  <si>
+    <t>embrace</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此，人工智能或许会给科学实践带来变革的想法是可行的。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但主要障碍来自社会：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有在人类科学家愿意并有能力运用这类工具时，它才有可能发生。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>许多人类科学家缺少技能与训练；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有些人担心失业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸运的是，还是有一些乐观的迹象。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能工具如今正在从由人工智能研究者大力推动转变为受到其他领域专家热烈欢迎。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Governments and funding bodies could help by pressing for greater use of common strandards to allow AI systems to exchange and interpret laboratory results and other data.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thet could also fund more research into the integration of AI smarts with laboratory robotics, and into forms of AI beyond those being pursued in the private sector, which has bet nearly all its chips on language-based systems like ChatGPT.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less fashionable forms of AI, such as, model-based machine learning, may be better suited to scientific tasks such as forming hypotheses.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bodies</t>
+  </si>
+  <si>
+    <t>body</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pressing for</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>press</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>integration</t>
+  </si>
+  <si>
+    <t>integration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>smarts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>robotics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chip</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The adding of the artificial</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>政府与融资机构也能帮上忙，例如大力敦促更多地使用共同标准，使人工智能得以用来交流并解读实验室结果和其他数据。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们还可以资助更多研究，从而促进人工智能的智力与实验室机器人技术相融合，以及研究那些未受私营部门追捧的人工智能类型。私营部门几乎将所有筹码都押注在了ChatGPT这类以语言为基础的人工智能系统之上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不那么流行的人工智能类型，例如以模型为基础的机器学习，或许更适合像提出假设这样的科学任务。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工造物的添加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 1655, during a period of repid scientific progress, Robert Hooke, an English polymath, described the advent of new scientific instruments such as the microscope and telescope as "the adding of artificial organs to the natural".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>They let researchers explore previously inaccessible realms and discover things in new ways, "with prodigious benefit to all sorts of useful knowledge".</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For Hooke's modern-day successors, the adding of artificial intelligence to the scientific toolkit is poised to do the same in the coming years - with similarly world-changing results.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>polymath</t>
+  </si>
+  <si>
+    <t>advent</t>
+  </si>
+  <si>
+    <t>organs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>organ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>inaccessible</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>realms</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>realm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>prodigious</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>successors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>successor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>toolkit</t>
+  </si>
+  <si>
+    <t>poised</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>poise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1655年，在那段科学快速发展的时期，英国博学家罗伯特·胡克曾将显微镜与望远镜这类新型科学工具的出现描述为“为人体添加人工器官”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>它们让研究者得以探索此前无法触及的领域，并以新的方式发现事物，“给所有类型的有用知识都带来了巨大好处”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对胡克的现代后继者而言，在科学工具箱中添加人工智能也有望在未来几年产生同样的效果-也将取得类似的改变世界的成果。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI And Culture: The Dawn Of The Omnistar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能与文化：全能明星将至</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dawn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dawn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Omnistar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>omnistar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>set off</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>set</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这些都是喜人的成果。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>但学术期刊和实验室产生的影响可不止于此：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>它们使人员与思想能够以新的方式和更大的规模实现融合，从而改变了科学实践本身，解锁了更多能够取得发现的强大工具。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能同样也有引发这种转变的潜力。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Two areas in particular look promising.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The first is "literature-based discovery"(LBD), which involves analysing existing scientific literature, using ChatGPT-style language analysis, to look for new hypotheses, connections or ideas that humans may have missed.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBD us showing promise un udentufyung new experiments to try - and even suggesting potential research collaborators.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>This could stimulate interdisciplinary work and foster innovation at the boundaries between fields.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBD systems can also identify "blind spots" in given field, and even predict future discoveries and who will make them.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>literature</t>
-  </si>
-  <si>
-    <t>hypotheses</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hypothesis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>suggesting</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>suggest</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>stimulate</t>
-  </si>
-  <si>
-    <t>interdisciplinary</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>foster</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>boundaries</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>boundary</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fields</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>field</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>blind spots</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>blind spot</t>
-  </si>
-  <si>
-    <t>blind//spot</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The second area is "robot scientists", also known as "self-driving labs".</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>These are robotic systems that use AI to from new hypotheses, based on anlysis of existing data and literature, and then test those hypotheses bu performing hundreds or thousands of experiments, in fileds incliding systems biology and materials science.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unlike human scientists, robots are less attached to previous results, less driven by bias - and, crucially, easy to replicate.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>They could scale up experimental research, develop unexpected theories and explore avenues that human investigators might not have considered.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>systems biology</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>biology</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>attached</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>replicate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>scale up</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>avenues</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>avenue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>有两个领域看起来尤为有前景。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>首先是“基于文献的发现”（LBD），这包含分析现有科学文献，使用类似ChatGPT的语言分析方式来寻找人们可能未察觉到的新假设、新联系或者新想法。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBD在确定可尝试的新实验方面正展现出潜力-它甚至能够推荐潜在的研究合作者。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这有可能促进跨学科研究，并在不同学科的交叉领域培育创新。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LBD系统还可以识别特定领域的“盲点”，甚至预测未来的发现以及发现者。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二个领域是“机器人科学家”，它们也被称为“自驱型实验室”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>这些机器人系统以对现有数据和文献的分析为基础，使用人工智能来形成新的假设，然后通过开展数百数千次实验来验证这些假设，涉及领域包括系统生物学和材料科学等。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>与人类科学家不同，机器人受以往研究结果的牵绊更少，受偏见的影响也要更小-关键是其容易复制。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>它们可以扩大实验性研究的规模，发展出意想不到的理论，并探索人类研究者或许从未思考过的道路。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The idea that AI might transform scientific practice is therefore feasible.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>But the main barrier is sociological:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>it can happen only if human scientists are willing and able to use such tools.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Many lack skills and training;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>some worry about being put out of a job.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fortunately, there are hopeful signs.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI tools are now moving from being pushed by AI researchers to being embraced by specialists in other fields.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>feasible</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sociological</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>embraced</t>
-  </si>
-  <si>
-    <t>embrace</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>因此，人工智能或许会给科学实践带来变革的想法是可行的。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>但主要障碍来自社会：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有在人类科学家愿意并有能力运用这类工具时，它才有可能发生。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>许多人类科学家缺少技能与训练；</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>有些人担心失业。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>幸运的是，还是有一些乐观的迹象。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能工具如今正在从由人工智能研究者大力推动转变为受到其他领域专家热烈欢迎。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Governments and funding bodies could help by pressing for greater use of common strandards to allow AI systems to exchange and interpret laboratory results and other data.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thet could also fund more research into the integration of AI smarts with laboratory robotics, and into forms of AI beyond those being pursued in the private sector, which has bet nearly all its chips on language-based systems like ChatGPT.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less fashionable forms of AI, such as, model-based machine learning, may be better suited to scientific tasks such as forming hypotheses.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bodies</t>
-  </si>
-  <si>
-    <t>body</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pressing for</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>press</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>press for sth.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>integration</t>
-  </si>
-  <si>
-    <t>integration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>smarts</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>robotics</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>chips</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>chip</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The adding of the artificial</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>政府与融资机构也能帮上忙，例如大力敦促更多地使用共同标准，使人工智能得以用来交流并解读实验室结果和其他数据。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>它们还可以资助更多研究，从而促进人工智能的智力与实验室机器人技术相融合，以及研究那些未受私营部门追捧的人工智能类型。私营部门几乎将所有筹码都押注在了ChatGPT这类以语言为基础的人工智能系统之上</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不那么流行的人工智能类型，例如以模型为基础的机器学习，或许更适合像提出假设这样的科学任务。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工造物的添加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>In 1655, during a period of repid scientific progress, Robert Hooke, an English polymath, described the advent of new scientific instruments such as the microscope and telescope as "the adding of artificial organs to the natural".</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>They let researchers explore previously inaccessible realms and discover things in new ways, "with prodigious benefit to all sorts of useful knowledge".</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>For Hooke's modern-day successors, the adding of artificial intelligence to the scientific toolkit is poised to do the same in the coming years - with similarly world-changing results.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>polymath</t>
-  </si>
-  <si>
-    <t>advent</t>
-  </si>
-  <si>
-    <t>organs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>organ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>inaccessible</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>realms</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>realm</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>prodigious</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>successors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>successor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>toolkit</t>
-  </si>
-  <si>
-    <t>poised</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>poise</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1655年，在那段科学快速发展的时期，英国博学家罗伯特·胡克曾将显微镜与望远镜这类新型科学工具的出现描述为“为人体添加人工器官”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>它们让研究者得以探索此前无法触及的领域，并以新的方式发现事物，“给所有类型的有用知识都带来了巨大好处”。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对胡克的现代后继者而言，在科学工具箱中添加人工智能也有望在未来几年产生同样的效果-也将取得类似的改变世界的成果。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI And Culture: The Dawn Of The Omnistar</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能与文化：全能明星将至</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dawn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dawn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Omnistar</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>omnistar</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mechanism</t>
+  </si>
+  <si>
+    <t>indeed</t>
+  </si>
+  <si>
+    <t>favour</t>
+  </si>
+  <si>
+    <t>observation</t>
+  </si>
+  <si>
+    <t>observations</t>
+  </si>
+  <si>
+    <t>journal</t>
+  </si>
+  <si>
+    <t>journals</t>
+  </si>
+  <si>
+    <t>In the 17th century microscopes and telescopes opened up new vistas of discovery and encouraged researchers to favour their own observations over the received wisdom of antiquity, while the introduction of scientific journals gave them new ways to share and publicise their finding.</t>
+  </si>
+  <si>
+    <t>rapid</t>
+  </si>
+  <si>
+    <t>particular</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1190,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1202,9 +1232,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1483,15 +1514,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1508,7 +1539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1525,7 +1556,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1542,7 +1573,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="30">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1559,7 +1590,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1570,13 +1601,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1593,7 +1624,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1610,7 +1641,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1627,7 +1658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1644,7 +1675,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1661,7 +1692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1678,7 +1709,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1695,7 +1726,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="30">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1712,7 +1743,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1729,7 +1760,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="60">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1746,7 +1777,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="60">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1757,13 +1788,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1774,13 +1805,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="60">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1791,13 +1822,13 @@
         <v>4</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1808,13 +1839,13 @@
         <v>4</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1825,13 +1856,13 @@
         <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="30">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1842,13 +1873,13 @@
         <v>5</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1859,13 +1890,13 @@
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1876,13 +1907,13 @@
         <v>5</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1893,13 +1924,13 @@
         <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1910,13 +1941,13 @@
         <v>5</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="30">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1927,13 +1958,13 @@
         <v>5</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="30">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1944,13 +1975,13 @@
         <v>5</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1961,13 +1992,13 @@
         <v>6</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1978,13 +2009,13 @@
         <v>6</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1995,13 +2026,13 @@
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2012,13 +2043,13 @@
         <v>6</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2029,13 +2060,13 @@
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="45">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2046,13 +2077,13 @@
         <v>7</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="30">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2063,13 +2094,13 @@
         <v>7</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="30">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2080,13 +2111,13 @@
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="30">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2097,13 +2128,13 @@
         <v>7</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2114,13 +2145,13 @@
         <v>8</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="45">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2131,13 +2162,13 @@
         <v>8</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2148,13 +2179,13 @@
         <v>8</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="30">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2165,13 +2196,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2182,13 +2213,13 @@
         <v>9</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2199,13 +2230,13 @@
         <v>9</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2216,13 +2247,13 @@
         <v>9</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2233,13 +2264,13 @@
         <v>9</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2250,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2267,13 +2298,13 @@
         <v>9</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="30">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2284,13 +2315,13 @@
         <v>9</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="45">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2301,13 +2332,13 @@
         <v>10</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="45">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2318,13 +2349,13 @@
         <v>10</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="30">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2335,13 +2366,13 @@
         <v>10</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2352,13 +2383,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:5" ht="45">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2369,13 +2400,13 @@
         <v>12</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="30">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2386,13 +2417,13 @@
         <v>12</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="45">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2403,10 +2434,10 @@
         <v>12</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -2417,17 +2448,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C86412D-EF50-4A2E-8A10-147D1E09B5C3}">
-  <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F121"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.9">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -2441,10 +2472,10 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13.9">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2461,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="13.9">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2475,7 +2506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="13.9">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2486,7 +2517,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.9">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2497,7 +2528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="13.9">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2508,7 +2539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="13.9">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2522,18 +2553,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="13.9">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.9">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2547,7 +2578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="13.9">
       <c r="A10">
         <v>3</v>
       </c>
@@ -2561,7 +2592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.9">
       <c r="A11">
         <v>3</v>
       </c>
@@ -2575,7 +2606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="13.9">
       <c r="A12">
         <v>3</v>
       </c>
@@ -2589,7 +2620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="13.9">
       <c r="A13">
         <v>4</v>
       </c>
@@ -2603,12 +2634,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="13.9">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2620,7 +2651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="13.9">
       <c r="A15">
         <v>4</v>
       </c>
@@ -2634,40 +2665,40 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.9">
       <c r="A16">
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" t="s">
         <v>151</v>
       </c>
-      <c r="D16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" ht="13.9">
       <c r="A17">
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="13.9">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13.9">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2681,19 +2712,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="13.9">
       <c r="A20">
         <v>6</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="13.9">
       <c r="A21">
         <v>7</v>
       </c>
@@ -2707,7 +2738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="13.9">
       <c r="A22">
         <v>7</v>
       </c>
@@ -2721,29 +2752,29 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23">
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="13.9">
       <c r="A24">
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="13.9">
       <c r="A25">
         <v>7</v>
       </c>
@@ -2757,18 +2788,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="13.9">
       <c r="A26">
         <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27">
         <v>8</v>
       </c>
@@ -2782,7 +2813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="13.9">
       <c r="A28">
         <v>8</v>
       </c>
@@ -2796,29 +2827,29 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="13.9">
       <c r="A29">
         <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.9">
       <c r="A30">
         <v>10</v>
       </c>
       <c r="B30" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" t="s">
         <v>158</v>
       </c>
-      <c r="D30" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" ht="13.9">
       <c r="A31">
         <v>10</v>
       </c>
@@ -2832,7 +2863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="13.9">
       <c r="A32">
         <v>11</v>
       </c>
@@ -2846,7 +2877,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="13.9">
       <c r="A33">
         <v>11</v>
       </c>
@@ -2860,7 +2891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34">
         <v>12</v>
       </c>
@@ -2874,7 +2905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="13.9">
       <c r="A35">
         <v>12</v>
       </c>
@@ -2888,7 +2919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="13.9">
       <c r="A36">
         <v>12</v>
       </c>
@@ -2902,7 +2933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="13.9">
       <c r="A37">
         <v>13</v>
       </c>
@@ -2916,7 +2947,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="13.9">
       <c r="A38">
         <v>13</v>
       </c>
@@ -2930,7 +2961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>13</v>
       </c>
@@ -2944,1110 +2975,1187 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>298</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="F41">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="F42">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>14</v>
       </c>
       <c r="B43" t="s">
+        <v>299</v>
+      </c>
+      <c r="D43" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="13.9">
+      <c r="A45">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
         <v>75</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D45" t="s">
         <v>76</v>
       </c>
-      <c r="F43">
+      <c r="F45">
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" t="s">
-        <v>84</v>
-      </c>
-      <c r="F44">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="13.9">
       <c r="A46">
         <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F46">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="13.9">
       <c r="A47">
         <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="F47">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F48">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>15</v>
       </c>
       <c r="B49" t="s">
+        <v>300</v>
+      </c>
+      <c r="D49" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>15</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D50" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>175</v>
+      </c>
+      <c r="F51">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>15</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D53" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>16</v>
+      </c>
+      <c r="B55" t="s">
+        <v>306</v>
+      </c>
+      <c r="D55" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>16</v>
+      </c>
+      <c r="B56" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D56" t="s">
         <v>90</v>
       </c>
-      <c r="F49">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="F56">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="13.9">
+      <c r="A57">
         <v>16</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B57" t="s">
         <v>91</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D57" t="s">
         <v>91</v>
       </c>
-      <c r="F50">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="F57">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="13.9">
+      <c r="A58">
         <v>16</v>
       </c>
-      <c r="B51" t="s">
-        <v>92</v>
-      </c>
-      <c r="D51" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="B58" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>163</v>
+      </c>
+      <c r="F58">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="13.9">
+      <c r="A59">
         <v>16</v>
       </c>
-      <c r="B52" t="s">
-        <v>165</v>
-      </c>
-      <c r="C52">
+      <c r="B59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59">
         <v>1</v>
       </c>
-      <c r="D52" t="s">
-        <v>164</v>
-      </c>
-      <c r="F52">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>16</v>
-      </c>
-      <c r="B53" t="s">
-        <v>161</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>163</v>
-      </c>
-      <c r="F53">
+      <c r="D59" t="s">
+        <v>162</v>
+      </c>
+      <c r="F59">
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>17</v>
-      </c>
-      <c r="B54" t="s">
-        <v>95</v>
-      </c>
-      <c r="D54" t="s">
-        <v>95</v>
-      </c>
-      <c r="F54">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>17</v>
-      </c>
-      <c r="B55" t="s">
-        <v>173</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" t="s">
-        <v>171</v>
-      </c>
-      <c r="F55">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>17</v>
-      </c>
-      <c r="B56" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" t="s">
-        <v>175</v>
-      </c>
-      <c r="F56">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>17</v>
-      </c>
-      <c r="B57" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>17</v>
-      </c>
-      <c r="B58" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" t="s">
-        <v>100</v>
-      </c>
-      <c r="F58">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>17</v>
-      </c>
-      <c r="B59" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" t="s">
-        <v>101</v>
-      </c>
-      <c r="F59">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="13.9">
       <c r="A60">
         <v>17</v>
       </c>
       <c r="B60" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="13.9">
+      <c r="A61">
+        <v>17</v>
+      </c>
+      <c r="B61" t="s">
+        <v>172</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" t="s">
+        <v>170</v>
+      </c>
+      <c r="F61">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="13.9">
+      <c r="A62">
+        <v>17</v>
+      </c>
+      <c r="B62" t="s">
         <v>169</v>
       </c>
-      <c r="C60">
+      <c r="C62">
         <v>1</v>
       </c>
-      <c r="D60" t="s">
-        <v>102</v>
-      </c>
-      <c r="F60">
+      <c r="D62" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" t="s">
+        <v>174</v>
+      </c>
+      <c r="F62">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="13.9">
+      <c r="A63">
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="13.9">
+      <c r="A64">
+        <v>17</v>
+      </c>
+      <c r="B64" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="13.9">
+      <c r="A65">
+        <v>17</v>
+      </c>
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" t="s">
+        <v>100</v>
+      </c>
+      <c r="F65">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66">
+        <v>17</v>
+      </c>
+      <c r="B66" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F66">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61">
+    <row r="67" spans="1:6" ht="13.9">
+      <c r="A67">
         <v>18</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" t="s">
+        <v>103</v>
+      </c>
+      <c r="F67">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="13.9">
+      <c r="A68">
+        <v>18</v>
+      </c>
+      <c r="B68" t="s">
         <v>105</v>
       </c>
-      <c r="D61" t="s">
-        <v>104</v>
-      </c>
-      <c r="F61">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62">
+      <c r="D68" t="s">
+        <v>105</v>
+      </c>
+      <c r="F68">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="13.9">
+      <c r="A69">
         <v>18</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B69" t="s">
         <v>106</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D69" t="s">
         <v>106</v>
       </c>
-      <c r="F62">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>18</v>
-      </c>
-      <c r="B63" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" t="s">
-        <v>107</v>
-      </c>
-      <c r="F63">
+      <c r="F69">
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64">
+    <row r="70" spans="1:6" ht="13.9">
+      <c r="A70">
         <v>20</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
+        <v>112</v>
+      </c>
+      <c r="F70">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="13.9">
+      <c r="A71">
+        <v>21</v>
+      </c>
+      <c r="B71" t="s">
         <v>113</v>
       </c>
-      <c r="D64" t="s">
-        <v>113</v>
-      </c>
-      <c r="F64">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65">
+      <c r="D71" t="s">
+        <v>114</v>
+      </c>
+      <c r="F71">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72">
         <v>21</v>
       </c>
-      <c r="B65" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="B72" t="s">
         <v>115</v>
       </c>
-      <c r="F65">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>21</v>
-      </c>
-      <c r="B66" t="s">
-        <v>116</v>
-      </c>
-      <c r="D66" t="s">
-        <v>116</v>
-      </c>
-      <c r="F66">
+      <c r="D72" t="s">
+        <v>115</v>
+      </c>
+      <c r="F72">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67">
+    <row r="73" spans="1:6" ht="13.9">
+      <c r="A73">
         <v>23</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B73" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" t="s">
+        <v>118</v>
+      </c>
+      <c r="F73">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="13.9">
+      <c r="A74">
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
         <v>119</v>
       </c>
-      <c r="D67" t="s">
-        <v>119</v>
-      </c>
-      <c r="F67">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68">
+      <c r="D74" t="s">
+        <v>120</v>
+      </c>
+      <c r="F74">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
         <v>23</v>
       </c>
-      <c r="B68" t="s">
-        <v>120</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="B75" t="s">
         <v>121</v>
       </c>
-      <c r="F68">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="D75" t="s">
+        <v>122</v>
+      </c>
+      <c r="F75">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
         <v>23</v>
       </c>
-      <c r="B69" t="s">
-        <v>122</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="B76" t="s">
+        <v>307</v>
+      </c>
+      <c r="D76" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>23</v>
+      </c>
+      <c r="B77" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77" t="s">
+        <v>178</v>
+      </c>
+      <c r="F77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="13.9">
+      <c r="A79">
+        <v>23</v>
+      </c>
+      <c r="B79" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
         <v>123</v>
       </c>
-      <c r="F69">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>23</v>
-      </c>
-      <c r="B70" t="s">
-        <v>178</v>
-      </c>
-      <c r="D70" t="s">
-        <v>179</v>
-      </c>
-      <c r="F70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>23</v>
-      </c>
-      <c r="B71" t="s">
-        <v>180</v>
-      </c>
-      <c r="D71" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>23</v>
-      </c>
-      <c r="B72" t="s">
-        <v>168</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72" t="s">
-        <v>124</v>
-      </c>
-      <c r="F72">
+      <c r="F79">
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73">
+    <row r="80" spans="1:6" ht="13.9">
+      <c r="A80">
         <v>24</v>
       </c>
-      <c r="B73" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73" t="s">
-        <v>134</v>
-      </c>
-      <c r="F73">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>24</v>
-      </c>
-      <c r="B74" t="s">
-        <v>135</v>
-      </c>
-      <c r="D74" t="s">
-        <v>135</v>
-      </c>
-      <c r="F74">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>24</v>
-      </c>
-      <c r="B75" t="s">
-        <v>136</v>
-      </c>
-      <c r="D75" t="s">
-        <v>137</v>
-      </c>
-      <c r="F75">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>24</v>
-      </c>
-      <c r="B76" t="s">
-        <v>138</v>
-      </c>
-      <c r="D76" t="s">
-        <v>139</v>
-      </c>
-      <c r="F76">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>25</v>
-      </c>
-      <c r="B77" t="s">
-        <v>167</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77" t="s">
-        <v>140</v>
-      </c>
-      <c r="F77">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>25</v>
-      </c>
-      <c r="B78" t="s">
-        <v>141</v>
-      </c>
-      <c r="D78" t="s">
-        <v>142</v>
-      </c>
-      <c r="F78">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>26</v>
-      </c>
-      <c r="B79" t="s">
-        <v>144</v>
-      </c>
-      <c r="D79" t="s">
-        <v>145</v>
-      </c>
-      <c r="F79">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>26</v>
-      </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
+        <v>133</v>
+      </c>
+      <c r="F80">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="13.9">
+      <c r="A81">
+        <v>24</v>
+      </c>
+      <c r="B81" t="s">
+        <v>134</v>
+      </c>
+      <c r="D81" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="13.9">
+      <c r="A82">
+        <v>24</v>
+      </c>
+      <c r="B82" t="s">
+        <v>135</v>
+      </c>
+      <c r="D82" t="s">
+        <v>136</v>
+      </c>
+      <c r="F82">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="13.9">
+      <c r="A83">
+        <v>24</v>
+      </c>
+      <c r="B83" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" t="s">
+        <v>138</v>
+      </c>
+      <c r="F83">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>139</v>
+      </c>
+      <c r="F84">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="13.9">
+      <c r="A85">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" t="s">
+        <v>141</v>
+      </c>
+      <c r="F85">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="13.9">
+      <c r="A86">
+        <v>26</v>
+      </c>
+      <c r="B86" t="s">
         <v>143</v>
       </c>
-      <c r="F80">
+      <c r="D86" t="s">
+        <v>144</v>
+      </c>
+      <c r="F86">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="13.9">
+      <c r="A87">
+        <v>26</v>
+      </c>
+      <c r="B87" t="s">
+        <v>165</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>142</v>
+      </c>
+      <c r="F87">
         <v>71</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81">
+    <row r="88" spans="1:6" ht="13.9">
+      <c r="A88">
         <v>29</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B88" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" t="s">
+        <v>189</v>
+      </c>
+      <c r="F88">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89">
+        <v>30</v>
+      </c>
+      <c r="B89" t="s">
+        <v>295</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
         <v>190</v>
       </c>
-      <c r="D81" t="s">
-        <v>190</v>
-      </c>
-      <c r="F81">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>30</v>
-      </c>
-      <c r="B82" t="s">
-        <v>191</v>
-      </c>
-      <c r="C82">
+      <c r="F89">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="13.9">
+      <c r="A90">
+        <v>32</v>
+      </c>
+      <c r="B90" t="s">
+        <v>200</v>
+      </c>
+      <c r="D90" t="s">
+        <v>200</v>
+      </c>
+      <c r="F90">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="13.9">
+      <c r="A91">
+        <v>32</v>
+      </c>
+      <c r="B91" t="s">
+        <v>201</v>
+      </c>
+      <c r="D91" t="s">
+        <v>202</v>
+      </c>
+      <c r="F91">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="13.9">
+      <c r="A92">
+        <v>33</v>
+      </c>
+      <c r="B92" t="s">
+        <v>203</v>
+      </c>
+      <c r="D92" t="s">
+        <v>204</v>
+      </c>
+      <c r="F92">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="13.9">
+      <c r="A93">
+        <v>34</v>
+      </c>
+      <c r="B93" t="s">
+        <v>205</v>
+      </c>
+      <c r="D93" t="s">
+        <v>205</v>
+      </c>
+      <c r="F93">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="13.9">
+      <c r="A94">
+        <v>34</v>
+      </c>
+      <c r="B94" t="s">
+        <v>206</v>
+      </c>
+      <c r="D94" t="s">
+        <v>206</v>
+      </c>
+      <c r="F94">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95">
+        <v>34</v>
+      </c>
+      <c r="B95" t="s">
+        <v>207</v>
+      </c>
+      <c r="D95" t="s">
+        <v>207</v>
+      </c>
+      <c r="F95">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="13.9">
+      <c r="A96">
+        <v>34</v>
+      </c>
+      <c r="B96" t="s">
+        <v>208</v>
+      </c>
+      <c r="D96" t="s">
+        <v>209</v>
+      </c>
+      <c r="F96">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="13.9">
+      <c r="A97">
+        <v>34</v>
+      </c>
+      <c r="B97" t="s">
+        <v>210</v>
+      </c>
+      <c r="D97" t="s">
+        <v>211</v>
+      </c>
+      <c r="F97">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="13.9">
+      <c r="A98">
+        <v>35</v>
+      </c>
+      <c r="B98" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98">
         <v>1</v>
       </c>
-      <c r="D82" t="s">
-        <v>192</v>
-      </c>
-      <c r="F82">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>32</v>
-      </c>
-      <c r="B83" t="s">
-        <v>202</v>
-      </c>
-      <c r="D83" t="s">
-        <v>202</v>
-      </c>
-      <c r="F83">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>32</v>
-      </c>
-      <c r="B84" t="s">
-        <v>203</v>
-      </c>
-      <c r="D84" t="s">
-        <v>204</v>
-      </c>
-      <c r="F84">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>33</v>
-      </c>
-      <c r="B85" t="s">
-        <v>205</v>
-      </c>
-      <c r="D85" t="s">
-        <v>206</v>
-      </c>
-      <c r="F85">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>34</v>
-      </c>
-      <c r="B86" t="s">
-        <v>207</v>
-      </c>
-      <c r="D86" t="s">
-        <v>207</v>
-      </c>
-      <c r="F86">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>34</v>
-      </c>
-      <c r="B87" t="s">
-        <v>208</v>
-      </c>
-      <c r="D87" t="s">
-        <v>208</v>
-      </c>
-      <c r="F87">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>34</v>
-      </c>
-      <c r="B88" t="s">
-        <v>209</v>
-      </c>
-      <c r="D88" t="s">
-        <v>209</v>
-      </c>
-      <c r="F88">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>34</v>
-      </c>
-      <c r="B89" t="s">
-        <v>210</v>
-      </c>
-      <c r="D89" t="s">
-        <v>211</v>
-      </c>
-      <c r="F89">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>34</v>
-      </c>
-      <c r="B90" t="s">
-        <v>212</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="D98" t="s">
+        <v>214</v>
+      </c>
+      <c r="E98" t="s">
         <v>213</v>
       </c>
-      <c r="F90">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>35</v>
-      </c>
-      <c r="B91" t="s">
-        <v>214</v>
-      </c>
-      <c r="C91">
+      <c r="F98">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="13.9">
+      <c r="A99">
+        <v>37</v>
+      </c>
+      <c r="B99" t="s">
+        <v>296</v>
+      </c>
+      <c r="C99">
         <v>1</v>
       </c>
-      <c r="D91" t="s">
-        <v>216</v>
-      </c>
-      <c r="E91" t="s">
-        <v>215</v>
-      </c>
-      <c r="F91">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>37</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="D99" t="s">
+        <v>219</v>
+      </c>
+      <c r="F99">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="13.9">
+      <c r="A100">
+        <v>38</v>
+      </c>
+      <c r="B100" t="s">
+        <v>220</v>
+      </c>
+      <c r="D100" t="s">
+        <v>220</v>
+      </c>
+      <c r="F100">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="13.9">
+      <c r="A101">
+        <v>38</v>
+      </c>
+      <c r="B101" t="s">
         <v>221</v>
       </c>
-      <c r="C92">
+      <c r="D101" t="s">
+        <v>221</v>
+      </c>
+      <c r="F101">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="13.9">
+      <c r="A102">
+        <v>39</v>
+      </c>
+      <c r="B102" t="s">
+        <v>222</v>
+      </c>
+      <c r="C102">
         <v>1</v>
       </c>
-      <c r="D92" t="s">
-        <v>222</v>
-      </c>
-      <c r="F92">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>38</v>
-      </c>
-      <c r="B93" t="s">
+      <c r="D102" t="s">
+        <v>95</v>
+      </c>
+      <c r="F102">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="13.9">
+      <c r="A103">
+        <v>39</v>
+      </c>
+      <c r="B103" t="s">
         <v>223</v>
       </c>
-      <c r="D93" t="s">
-        <v>223</v>
-      </c>
-      <c r="F93">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>38</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="D103" t="s">
         <v>224</v>
       </c>
-      <c r="D94" t="s">
-        <v>224</v>
-      </c>
-      <c r="F94">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>39</v>
-      </c>
-      <c r="B95" t="s">
-        <v>225</v>
-      </c>
-      <c r="C95">
+      <c r="F103">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="13.9">
+      <c r="A104">
+        <v>40</v>
+      </c>
+      <c r="B104" t="s">
+        <v>241</v>
+      </c>
+      <c r="D104" t="s">
+        <v>241</v>
+      </c>
+      <c r="F104">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="13.9">
+      <c r="A105">
+        <v>41</v>
+      </c>
+      <c r="B105" t="s">
+        <v>242</v>
+      </c>
+      <c r="D105" t="s">
+        <v>242</v>
+      </c>
+      <c r="F105">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9">
+      <c r="A106">
+        <v>46</v>
+      </c>
+      <c r="B106" t="s">
+        <v>243</v>
+      </c>
+      <c r="D106" t="s">
+        <v>244</v>
+      </c>
+      <c r="F106">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="13.9">
+      <c r="A107">
+        <v>47</v>
+      </c>
+      <c r="B107" t="s">
+        <v>255</v>
+      </c>
+      <c r="D107" t="s">
+        <v>256</v>
+      </c>
+      <c r="F107">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="13.9">
+      <c r="A108">
+        <v>47</v>
+      </c>
+      <c r="B108" t="s">
+        <v>257</v>
+      </c>
+      <c r="C108">
         <v>1</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D108" t="s">
+        <v>258</v>
+      </c>
+      <c r="E108" t="s">
+        <v>297</v>
+      </c>
+      <c r="F108">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="13.9">
+      <c r="A109">
+        <v>48</v>
+      </c>
+      <c r="B109" t="s">
+        <v>260</v>
+      </c>
+      <c r="D109" t="s">
+        <v>259</v>
+      </c>
+      <c r="F109">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="13.9">
+      <c r="A110">
+        <v>48</v>
+      </c>
+      <c r="B110" t="s">
+        <v>261</v>
+      </c>
+      <c r="D110" t="s">
+        <v>261</v>
+      </c>
+      <c r="F110">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111">
+        <v>48</v>
+      </c>
+      <c r="B111" t="s">
+        <v>262</v>
+      </c>
+      <c r="D111" t="s">
+        <v>262</v>
+      </c>
+      <c r="F111">
         <v>96</v>
       </c>
-      <c r="F95">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>39</v>
-      </c>
-      <c r="B96" t="s">
-        <v>226</v>
-      </c>
-      <c r="D96" t="s">
-        <v>227</v>
-      </c>
-      <c r="F96">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>40</v>
-      </c>
-      <c r="B97" t="s">
-        <v>244</v>
-      </c>
-      <c r="D97" t="s">
-        <v>244</v>
-      </c>
-      <c r="F97">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>41</v>
-      </c>
-      <c r="B98" t="s">
-        <v>245</v>
-      </c>
-      <c r="D98" t="s">
-        <v>245</v>
-      </c>
-      <c r="F98">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>46</v>
-      </c>
-      <c r="B99" t="s">
-        <v>246</v>
-      </c>
-      <c r="D99" t="s">
-        <v>247</v>
-      </c>
-      <c r="F99">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>47</v>
-      </c>
-      <c r="B100" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100" t="s">
-        <v>259</v>
-      </c>
-      <c r="F100">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>47</v>
-      </c>
-      <c r="B101" t="s">
-        <v>260</v>
-      </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-      <c r="D101" t="s">
-        <v>261</v>
-      </c>
-      <c r="E101" t="s">
-        <v>262</v>
-      </c>
-      <c r="F101">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102">
+    </row>
+    <row r="112" spans="1:6" ht="13.9">
+      <c r="A112">
         <v>48</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B112" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" t="s">
         <v>264</v>
       </c>
-      <c r="D102" t="s">
-        <v>263</v>
-      </c>
-      <c r="F102">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>48</v>
-      </c>
-      <c r="B103" t="s">
-        <v>265</v>
-      </c>
-      <c r="D103" t="s">
-        <v>265</v>
-      </c>
-      <c r="F103">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>48</v>
-      </c>
-      <c r="B104" t="s">
-        <v>266</v>
-      </c>
-      <c r="D104" t="s">
-        <v>266</v>
-      </c>
-      <c r="F104">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>48</v>
-      </c>
-      <c r="B105" t="s">
-        <v>267</v>
-      </c>
-      <c r="D105" t="s">
-        <v>268</v>
-      </c>
-      <c r="F105">
+      <c r="F112">
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106">
+    <row r="113" spans="1:6" ht="13.9">
+      <c r="A113">
         <v>51</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B113" t="s">
+        <v>273</v>
+      </c>
+      <c r="D113" t="s">
+        <v>273</v>
+      </c>
+      <c r="F113">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="13.9">
+      <c r="A114">
+        <v>51</v>
+      </c>
+      <c r="B114" t="s">
+        <v>274</v>
+      </c>
+      <c r="D114" t="s">
+        <v>274</v>
+      </c>
+      <c r="F114">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="13.9">
+      <c r="A115">
+        <v>51</v>
+      </c>
+      <c r="B115" t="s">
+        <v>275</v>
+      </c>
+      <c r="D115" t="s">
+        <v>276</v>
+      </c>
+      <c r="F115">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116">
+        <v>52</v>
+      </c>
+      <c r="B116" t="s">
         <v>277</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D116" t="s">
         <v>277</v>
       </c>
-      <c r="F106">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>51</v>
-      </c>
-      <c r="B107" t="s">
+      <c r="F116">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="13.9">
+      <c r="A117">
+        <v>52</v>
+      </c>
+      <c r="B117" t="s">
         <v>278</v>
       </c>
-      <c r="D107" t="s">
-        <v>278</v>
-      </c>
-      <c r="F107">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>51</v>
-      </c>
-      <c r="B108" t="s">
+      <c r="D117" t="s">
         <v>279</v>
       </c>
-      <c r="D108" t="s">
+      <c r="F117">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="13.9">
+      <c r="A118">
+        <v>52</v>
+      </c>
+      <c r="B118" t="s">
         <v>280</v>
       </c>
-      <c r="F108">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>52</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="D118" t="s">
+        <v>280</v>
+      </c>
+      <c r="F118">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="13.9">
+      <c r="A119">
+        <v>53</v>
+      </c>
+      <c r="B119" t="s">
         <v>281</v>
       </c>
-      <c r="D109" t="s">
-        <v>281</v>
-      </c>
-      <c r="F109">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>52</v>
-      </c>
-      <c r="B110" t="s">
+      <c r="D119" t="s">
         <v>282</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F119">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="13.9">
+      <c r="A120">
+        <v>53</v>
+      </c>
+      <c r="B120" t="s">
         <v>283</v>
       </c>
-      <c r="F110">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>52</v>
-      </c>
-      <c r="B111" t="s">
+      <c r="D120" t="s">
+        <v>283</v>
+      </c>
+      <c r="F120">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121">
+        <v>53</v>
+      </c>
+      <c r="B121" t="s">
         <v>284</v>
       </c>
-      <c r="D111" t="s">
-        <v>284</v>
-      </c>
-      <c r="F111">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>53</v>
-      </c>
-      <c r="B112" t="s">
+      <c r="D121" t="s">
         <v>285</v>
       </c>
-      <c r="D112" t="s">
-        <v>286</v>
-      </c>
-      <c r="F112">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>53</v>
-      </c>
-      <c r="B113" t="s">
-        <v>287</v>
-      </c>
-      <c r="D113" t="s">
-        <v>287</v>
-      </c>
-      <c r="F113">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>53</v>
-      </c>
-      <c r="B114" t="s">
-        <v>288</v>
-      </c>
-      <c r="D114" t="s">
-        <v>289</v>
-      </c>
-      <c r="F114">
+      <c r="F121">
         <v>107</v>
       </c>
     </row>
@@ -4061,15 +4169,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB71F98-C214-4E2A-8F31-34FC50527B4A}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4086,7 +4194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4097,10 +4205,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4112,15 +4220,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F015AC71-3C0E-4B3C-9B3E-599310938E5F}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4134,41 +4242,41 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5">
       <c r="B26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5">
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
     </row>

--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9593C8-AEA9-4319-B193-20DB4720E1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9068D74C-F78F-4C5D-90AB-0C760F685EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50415" yWindow="5430" windowWidth="12360" windowHeight="14160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50415" yWindow="5430" windowWidth="12360" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
@@ -182,10 +182,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能如何能够给科学带来革命性的改变。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>有关人工智能的辩论通常倾向于聚焦在它的潜在危害上。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1158,6 +1154,9 @@
   </si>
   <si>
     <t>particular</t>
+  </si>
+  <si>
+    <t>人工智能如何能够给科学带来革命性的改变</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1570,7 +1569,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30">
@@ -1587,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30">
@@ -1601,10 +1600,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1621,7 +1620,7 @@
         <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1638,7 +1637,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30">
@@ -1655,7 +1654,7 @@
         <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30">
@@ -1672,7 +1671,7 @@
         <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1689,7 +1688,7 @@
         <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30">
@@ -1703,10 +1702,10 @@
         <v>2</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1720,10 +1719,10 @@
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30">
@@ -1737,10 +1736,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1754,10 +1753,10 @@
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="60">
@@ -1771,10 +1770,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="60">
@@ -1788,10 +1787,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45">
@@ -1805,10 +1804,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="60">
@@ -1822,10 +1821,10 @@
         <v>4</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45">
@@ -1839,10 +1838,10 @@
         <v>4</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1856,10 +1855,10 @@
         <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30">
@@ -1873,10 +1872,10 @@
         <v>5</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30">
@@ -1890,10 +1889,10 @@
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1907,10 +1906,10 @@
         <v>5</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="45">
@@ -1924,10 +1923,10 @@
         <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="30">
@@ -1941,10 +1940,10 @@
         <v>5</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30">
@@ -1958,10 +1957,10 @@
         <v>5</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="30">
@@ -1975,10 +1974,10 @@
         <v>5</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1992,10 +1991,10 @@
         <v>6</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2009,10 +2008,10 @@
         <v>6</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="30">
@@ -2026,10 +2025,10 @@
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2043,10 +2042,10 @@
         <v>6</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2060,10 +2059,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45">
@@ -2077,10 +2076,10 @@
         <v>7</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="30">
@@ -2094,10 +2093,10 @@
         <v>7</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30">
@@ -2111,10 +2110,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30">
@@ -2128,10 +2127,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2145,10 +2144,10 @@
         <v>8</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="45">
@@ -2162,10 +2161,10 @@
         <v>8</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30">
@@ -2179,10 +2178,10 @@
         <v>8</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="30">
@@ -2196,10 +2195,10 @@
         <v>8</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2213,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2230,10 +2229,10 @@
         <v>9</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2247,10 +2246,10 @@
         <v>9</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2264,10 +2263,10 @@
         <v>9</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2281,10 +2280,10 @@
         <v>9</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2298,10 +2297,10 @@
         <v>9</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30">
@@ -2315,10 +2314,10 @@
         <v>9</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="45">
@@ -2332,10 +2331,10 @@
         <v>10</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="45">
@@ -2349,10 +2348,10 @@
         <v>10</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30">
@@ -2366,10 +2365,10 @@
         <v>10</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2383,10 +2382,10 @@
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="45">
@@ -2400,10 +2399,10 @@
         <v>12</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="30">
@@ -2417,10 +2416,10 @@
         <v>12</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="45">
@@ -2434,10 +2433,10 @@
         <v>12</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -2458,7 +2457,7 @@
     <col min="6" max="6" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.9">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -2472,10 +2471,10 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="13.9">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="13.9">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2506,7 +2505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="13.9">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2517,7 +2516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.9">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2528,7 +2527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="13.9">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="13.9">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2553,18 +2552,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="13.9">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="13.9">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2578,7 +2577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="13.9">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>3</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="13.9">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>3</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="13.9">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>3</v>
       </c>
@@ -2620,7 +2619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="13.9">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>4</v>
       </c>
@@ -2634,12 +2633,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="13.9">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2651,7 +2650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="13.9">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>4</v>
       </c>
@@ -2665,40 +2664,40 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="13.9">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" t="s">
         <v>150</v>
       </c>
-      <c r="D16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="13.9">
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="13.9">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="13.9">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2712,19 +2711,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="13.9">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>6</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="13.9">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>7</v>
       </c>
@@ -2738,7 +2737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="13.9">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>7</v>
       </c>
@@ -2752,29 +2751,29 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="13.9">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="13.9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="13.9">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>7</v>
       </c>
@@ -2788,18 +2787,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="13.9">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="13.9">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>8</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>8</v>
       </c>
@@ -2827,135 +2826,135 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.9">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="13.9">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>10</v>
       </c>
       <c r="B30" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" t="s">
         <v>157</v>
       </c>
-      <c r="D30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="13.9">
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F31">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="13.9">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>11</v>
       </c>
       <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" t="s">
         <v>56</v>
-      </c>
-      <c r="D32" t="s">
-        <v>57</v>
       </c>
       <c r="F32">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="13.9">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>11</v>
       </c>
       <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
         <v>58</v>
-      </c>
-      <c r="D33" t="s">
-        <v>59</v>
       </c>
       <c r="F33">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F34">
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="13.9">
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>12</v>
       </c>
       <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" t="s">
         <v>63</v>
-      </c>
-      <c r="D35" t="s">
-        <v>64</v>
       </c>
       <c r="F35">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="13.9">
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F36">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="13.9">
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>13</v>
       </c>
       <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" t="s">
         <v>66</v>
-      </c>
-      <c r="D37" t="s">
-        <v>67</v>
       </c>
       <c r="F37">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="13.9">
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38">
         <v>28</v>
@@ -2966,10 +2965,10 @@
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F39">
         <v>29</v>
@@ -2980,10 +2979,10 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2991,10 +2990,10 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F41">
         <v>30</v>
@@ -3005,10 +3004,10 @@
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F42">
         <v>31</v>
@@ -3019,10 +3018,10 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D43" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3030,55 +3029,55 @@
         <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F44">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="13.9">
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>14</v>
       </c>
       <c r="B45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45" t="s">
         <v>75</v>
-      </c>
-      <c r="D45" t="s">
-        <v>76</v>
       </c>
       <c r="F45">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="13.9">
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>15</v>
       </c>
       <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" t="s">
         <v>82</v>
-      </c>
-      <c r="D46" t="s">
-        <v>83</v>
       </c>
       <c r="F46">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="13.9">
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>15</v>
       </c>
       <c r="B47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
         <v>84</v>
-      </c>
-      <c r="D47" t="s">
-        <v>85</v>
       </c>
       <c r="F47">
         <v>35</v>
@@ -3089,10 +3088,10 @@
         <v>15</v>
       </c>
       <c r="B48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" t="s">
         <v>86</v>
-      </c>
-      <c r="D48" t="s">
-        <v>87</v>
       </c>
       <c r="F48">
         <v>36</v>
@@ -3103,10 +3102,10 @@
         <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3114,10 +3113,10 @@
         <v>15</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3125,13 +3124,13 @@
         <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F51">
         <v>37</v>
@@ -3142,10 +3141,10 @@
         <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F52">
         <v>38</v>
@@ -3156,10 +3155,10 @@
         <v>15</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3167,10 +3166,10 @@
         <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F54">
         <v>39</v>
@@ -3181,10 +3180,10 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D55" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3192,283 +3191,283 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F56">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="13.9">
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57">
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="13.9">
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F58">
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="13.9">
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F59">
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="13.9">
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F60">
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F61">
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="13.9">
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F62">
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="13.9">
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F63">
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="13.9">
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>17</v>
       </c>
       <c r="B64" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" t="s">
         <v>98</v>
-      </c>
-      <c r="D64" t="s">
-        <v>99</v>
       </c>
       <c r="F64">
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="13.9">
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F65">
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F66">
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="13.9">
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F67">
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="13.9">
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>18</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F68">
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="13.9">
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F69">
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="13.9">
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F70">
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>21</v>
       </c>
       <c r="B71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
         <v>113</v>
-      </c>
-      <c r="D71" t="s">
-        <v>114</v>
       </c>
       <c r="F71">
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="13.9">
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F72">
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="13.9">
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>23</v>
       </c>
       <c r="B73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F73">
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="13.9">
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>23</v>
       </c>
       <c r="B74" t="s">
+        <v>118</v>
+      </c>
+      <c r="D74" t="s">
         <v>119</v>
-      </c>
-      <c r="D74" t="s">
-        <v>120</v>
       </c>
       <c r="F74">
         <v>59</v>
@@ -3479,10 +3478,10 @@
         <v>23</v>
       </c>
       <c r="B75" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" t="s">
         <v>121</v>
-      </c>
-      <c r="D75" t="s">
-        <v>122</v>
       </c>
       <c r="F75">
         <v>60</v>
@@ -3493,10 +3492,10 @@
         <v>23</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D76" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3504,656 +3503,656 @@
         <v>23</v>
       </c>
       <c r="B77" t="s">
+        <v>176</v>
+      </c>
+      <c r="D77" t="s">
         <v>177</v>
-      </c>
-      <c r="D77" t="s">
-        <v>178</v>
       </c>
       <c r="F77">
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>23</v>
       </c>
       <c r="B78" t="s">
+        <v>178</v>
+      </c>
+      <c r="D78" t="s">
         <v>179</v>
       </c>
-      <c r="D78" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="13.9">
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>23</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F79">
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="13.9">
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F80">
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="13.9">
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>24</v>
       </c>
       <c r="B81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F81">
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="13.9">
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>24</v>
       </c>
       <c r="B82" t="s">
+        <v>134</v>
+      </c>
+      <c r="D82" t="s">
         <v>135</v>
-      </c>
-      <c r="D82" t="s">
-        <v>136</v>
       </c>
       <c r="F82">
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="13.9">
+    <row r="83" spans="1:6">
       <c r="A83">
         <v>24</v>
       </c>
       <c r="B83" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" t="s">
         <v>137</v>
-      </c>
-      <c r="D83" t="s">
-        <v>138</v>
       </c>
       <c r="F83">
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
+    <row r="84" spans="1:6">
       <c r="A84">
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F84">
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="13.9">
+    <row r="85" spans="1:6">
       <c r="A85">
         <v>25</v>
       </c>
       <c r="B85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" t="s">
         <v>140</v>
-      </c>
-      <c r="D85" t="s">
-        <v>141</v>
       </c>
       <c r="F85">
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="13.9">
+    <row r="86" spans="1:6">
       <c r="A86">
         <v>26</v>
       </c>
       <c r="B86" t="s">
+        <v>142</v>
+      </c>
+      <c r="D86" t="s">
         <v>143</v>
-      </c>
-      <c r="D86" t="s">
-        <v>144</v>
       </c>
       <c r="F86">
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="13.9">
+    <row r="87" spans="1:6">
       <c r="A87">
         <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F87">
         <v>71</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.9">
+    <row r="88" spans="1:6">
       <c r="A88">
         <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F88">
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="13.9">
+    <row r="89" spans="1:6">
       <c r="A89">
         <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F89">
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="13.9">
+    <row r="90" spans="1:6">
       <c r="A90">
         <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F90">
         <v>74</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="13.9">
+    <row r="91" spans="1:6">
       <c r="A91">
         <v>32</v>
       </c>
       <c r="B91" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" t="s">
         <v>201</v>
-      </c>
-      <c r="D91" t="s">
-        <v>202</v>
       </c>
       <c r="F91">
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="13.9">
+    <row r="92" spans="1:6">
       <c r="A92">
         <v>33</v>
       </c>
       <c r="B92" t="s">
+        <v>202</v>
+      </c>
+      <c r="D92" t="s">
         <v>203</v>
-      </c>
-      <c r="D92" t="s">
-        <v>204</v>
       </c>
       <c r="F92">
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="13.9">
+    <row r="93" spans="1:6">
       <c r="A93">
         <v>34</v>
       </c>
       <c r="B93" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D93" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F93">
         <v>77</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6">
       <c r="A94">
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D94" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F94">
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6">
       <c r="A95">
         <v>34</v>
       </c>
       <c r="B95" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D95" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F95">
         <v>79</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="13.9">
+    <row r="96" spans="1:6">
       <c r="A96">
         <v>34</v>
       </c>
       <c r="B96" t="s">
+        <v>207</v>
+      </c>
+      <c r="D96" t="s">
         <v>208</v>
-      </c>
-      <c r="D96" t="s">
-        <v>209</v>
       </c>
       <c r="F96">
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="13.9">
+    <row r="97" spans="1:6">
       <c r="A97">
         <v>34</v>
       </c>
       <c r="B97" t="s">
+        <v>209</v>
+      </c>
+      <c r="D97" t="s">
         <v>210</v>
-      </c>
-      <c r="D97" t="s">
-        <v>211</v>
       </c>
       <c r="F97">
         <v>81</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="13.9">
+    <row r="98" spans="1:6">
       <c r="A98">
         <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E98" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F98">
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="13.9">
+    <row r="99" spans="1:6">
       <c r="A99">
         <v>37</v>
       </c>
       <c r="B99" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F99">
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="13.9">
+    <row r="100" spans="1:6">
       <c r="A100">
         <v>38</v>
       </c>
       <c r="B100" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D100" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F100">
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="13.9">
+    <row r="101" spans="1:6">
       <c r="A101">
         <v>38</v>
       </c>
       <c r="B101" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D101" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F101">
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9">
+    <row r="102" spans="1:6">
       <c r="A102">
         <v>39</v>
       </c>
       <c r="B102" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F102">
         <v>87</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="13.9">
+    <row r="103" spans="1:6">
       <c r="A103">
         <v>39</v>
       </c>
       <c r="B103" t="s">
+        <v>222</v>
+      </c>
+      <c r="D103" t="s">
         <v>223</v>
-      </c>
-      <c r="D103" t="s">
-        <v>224</v>
       </c>
       <c r="F103">
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="13.9">
+    <row r="104" spans="1:6">
       <c r="A104">
         <v>40</v>
       </c>
       <c r="B104" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D104" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F104">
         <v>89</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="13.9">
+    <row r="105" spans="1:6">
       <c r="A105">
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D105" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F105">
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
+    <row r="106" spans="1:6">
       <c r="A106">
         <v>46</v>
       </c>
       <c r="B106" t="s">
+        <v>242</v>
+      </c>
+      <c r="D106" t="s">
         <v>243</v>
-      </c>
-      <c r="D106" t="s">
-        <v>244</v>
       </c>
       <c r="F106">
         <v>91</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="13.9">
+    <row r="107" spans="1:6">
       <c r="A107">
         <v>47</v>
       </c>
       <c r="B107" t="s">
+        <v>254</v>
+      </c>
+      <c r="D107" t="s">
         <v>255</v>
-      </c>
-      <c r="D107" t="s">
-        <v>256</v>
       </c>
       <c r="F107">
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="13.9">
+    <row r="108" spans="1:6">
       <c r="A108">
         <v>47</v>
       </c>
       <c r="B108" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C108">
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E108" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F108">
         <v>93</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="13.9">
+    <row r="109" spans="1:6">
       <c r="A109">
         <v>48</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F109">
         <v>94</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="13.9">
+    <row r="110" spans="1:6">
       <c r="A110">
         <v>48</v>
       </c>
       <c r="B110" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D110" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F110">
         <v>95</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
+    <row r="111" spans="1:6">
       <c r="A111">
         <v>48</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D111" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F111">
         <v>96</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="13.9">
+    <row r="112" spans="1:6">
       <c r="A112">
         <v>48</v>
       </c>
       <c r="B112" t="s">
+        <v>262</v>
+      </c>
+      <c r="D112" t="s">
         <v>263</v>
-      </c>
-      <c r="D112" t="s">
-        <v>264</v>
       </c>
       <c r="F112">
         <v>97</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="13.9">
+    <row r="113" spans="1:6">
       <c r="A113">
         <v>51</v>
       </c>
       <c r="B113" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D113" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F113">
         <v>99</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="13.9">
+    <row r="114" spans="1:6">
       <c r="A114">
         <v>51</v>
       </c>
       <c r="B114" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D114" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F114">
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="13.9">
+    <row r="115" spans="1:6">
       <c r="A115">
         <v>51</v>
       </c>
       <c r="B115" t="s">
+        <v>274</v>
+      </c>
+      <c r="D115" t="s">
         <v>275</v>
-      </c>
-      <c r="D115" t="s">
-        <v>276</v>
       </c>
       <c r="F115">
         <v>101</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="13.9">
+    <row r="116" spans="1:6">
       <c r="A116">
         <v>52</v>
       </c>
       <c r="B116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F116">
         <v>102</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="13.9">
+    <row r="117" spans="1:6">
       <c r="A117">
         <v>52</v>
       </c>
       <c r="B117" t="s">
+        <v>277</v>
+      </c>
+      <c r="D117" t="s">
         <v>278</v>
-      </c>
-      <c r="D117" t="s">
-        <v>279</v>
       </c>
       <c r="F117">
         <v>103</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="13.9">
+    <row r="118" spans="1:6">
       <c r="A118">
         <v>52</v>
       </c>
       <c r="B118" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D118" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F118">
         <v>104</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="13.9">
+    <row r="119" spans="1:6">
       <c r="A119">
         <v>53</v>
       </c>
       <c r="B119" t="s">
+        <v>280</v>
+      </c>
+      <c r="D119" t="s">
         <v>281</v>
-      </c>
-      <c r="D119" t="s">
-        <v>282</v>
       </c>
       <c r="F119">
         <v>105</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="13.9">
+    <row r="120" spans="1:6">
       <c r="A120">
         <v>53</v>
       </c>
       <c r="B120" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D120" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F120">
         <v>106</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6">
       <c r="A121">
         <v>53</v>
       </c>
       <c r="B121" t="s">
+        <v>283</v>
+      </c>
+      <c r="D121" t="s">
         <v>284</v>
-      </c>
-      <c r="D121" t="s">
-        <v>285</v>
       </c>
       <c r="F121">
         <v>107</v>
@@ -4205,10 +4204,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4242,7 +4241,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4250,10 +4249,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" t="s">
         <v>291</v>
-      </c>
-      <c r="D2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4261,10 +4260,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" t="s">
         <v>293</v>
-      </c>
-      <c r="D3" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="20" spans="2:5">

--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9068D74C-F78F-4C5D-90AB-0C760F685EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE503BA7-8F0C-49C6-A884-A2F1AD97BB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50415" yWindow="5430" windowWidth="12360" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11904" yWindow="12720" windowWidth="22188" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
@@ -1163,24 +1163,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1188,7 +1188,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1234,7 +1234,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1513,15 +1513,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30">
+    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="60">
+    <row r="15" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="60">
+    <row r="16" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="45">
+    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="60">
+    <row r="18" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="45">
+    <row r="19" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="30">
+    <row r="21" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="30">
+    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="45">
+    <row r="24" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="30">
+    <row r="25" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="30">
+    <row r="26" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="30">
+    <row r="27" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="45">
+    <row r="33" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="30">
+    <row r="34" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="30">
+    <row r="35" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="30">
+    <row r="36" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="45">
+    <row r="38" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="30">
+    <row r="47" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="45">
+    <row r="48" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="45">
+    <row r="49" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="30">
+    <row r="50" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="45">
+    <row r="52" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="30">
+    <row r="53" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="45">
+    <row r="54" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2448,16 +2448,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C86412D-EF50-4A2E-8A10-147D1E09B5C3}">
   <dimension ref="A1:F121"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>4</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>7</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>7</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>8</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>8</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>8</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>10</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>10</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>11</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>11</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>12</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>12</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>12</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>13</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>13</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>13</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>14</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>14</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>14</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>14</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>15</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>15</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>15</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>15</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>15</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>15</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>15</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>15</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>15</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>16</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>16</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>16</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>16</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>16</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>17</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>17</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>17</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>17</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>17</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>17</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>17</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>18</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>18</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>18</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>20</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>21</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>21</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>23</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>23</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>23</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>23</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>23</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>23</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>23</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>24</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>24</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>24</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>24</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>25</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>25</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>26</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>26</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>29</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>30</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>32</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>32</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>33</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>34</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>34</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>34</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>34</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>34</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>35</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>37</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>38</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>38</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>39</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>39</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>40</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>41</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>46</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>47</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>47</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>48</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>48</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>48</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>48</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>51</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>51</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>51</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>52</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>52</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>52</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>53</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>53</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>53</v>
       </c>
@@ -4168,15 +4168,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB71F98-C214-4E2A-8F31-34FC50527B4A}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4219,15 +4219,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F015AC71-3C0E-4B3C-9B3E-599310938E5F}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4266,16 +4266,16 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
     </row>

--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE503BA7-8F0C-49C6-A884-A2F1AD97BB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A558F5-3564-4380-B530-00AA1EAD4A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11904" yWindow="12720" windowWidth="22188" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32955" yWindow="-1395" windowWidth="28800" windowHeight="15885" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
     <sheet name="01_words" sheetId="2" r:id="rId2"/>
     <sheet name="02_contents" sheetId="3" r:id="rId3"/>
     <sheet name="02_words" sheetId="4" r:id="rId4"/>
+    <sheet name="03_contents" sheetId="5" r:id="rId5"/>
+    <sheet name="03_words" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="324">
   <si>
     <t>type</t>
   </si>
@@ -1157,30 +1159,78 @@
   </si>
   <si>
     <t>人工智能如何能够给科学带来革命性的改变</t>
+  </si>
+  <si>
+    <t>Moving dynamically into the future</t>
+  </si>
+  <si>
+    <t>The transition to software-defined vehicles (SDVs) with centralized E/E architectures marks a fundamental shift in the automotive landscape by decoupling hardware and software.</t>
+  </si>
+  <si>
+    <t>向采用集中式电子电气架构的软件定义汽车 (SDV) 的过渡，标志着汽车领域硬件和软件解耦的根本性转变。</t>
+  </si>
+  <si>
+    <t>Paired with new drive technologies the mobility sector is reconstituting itself with new business chances but also with challenges.</t>
+  </si>
+  <si>
+    <t>随着新型驱动技术的出现，移动出行行业正在重塑自身，带来新的商机，但也面临挑战。</t>
+  </si>
+  <si>
+    <t>China has become the fastest market in terms of speed of innovation.</t>
+  </si>
+  <si>
+    <t>中国已成为创新速度最快的市场。</t>
+  </si>
+  <si>
+    <t>As consequence the speed and scope of the whole sector are unprecedented as many new players enter the market and create intense competitive and cost pressure.</t>
+  </si>
+  <si>
+    <t>因此，整个行业的发展速度和规模都是前所未有的，因为许多新参与者进入市场，造成了激烈的竞争和成本压力。</t>
+  </si>
+  <si>
+    <t>Weak economic growth in key markets, and increasing trade barriers make the situation even more challenging.</t>
+  </si>
+  <si>
+    <t>主要市场经济增长乏力，贸易壁垒日益增加，使形势更加严峻。</t>
+  </si>
+  <si>
+    <t>The different regional requirements and framework conditions lead to a varying pace in the introduction of new technologies such as electromobility, automated driving or E/E architectures.</t>
+  </si>
+  <si>
+    <t>不同的区域要求和框架条件导致电动汽车、自动驾驶或电子电气架构等新技术的引入速度各不相同。</t>
+  </si>
+  <si>
+    <t>A deep and broad understanding of BBM markets and customers is thus an indispensable first step to define our direction.</t>
+  </si>
+  <si>
+    <t>因此，深入了解 BBM 市场和客户是确定我们发展方向的必要第一步。</t>
+  </si>
+  <si>
+    <t>充满活力 迈向未来</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1188,7 +1238,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1219,7 +1269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1232,9 +1282,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1513,15 +1565,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1538,7 +1590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1555,7 +1607,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1572,7 +1624,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="30">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1589,7 +1641,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1606,7 +1658,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1623,7 +1675,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1640,7 +1692,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1657,7 +1709,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1674,7 +1726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1691,7 +1743,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1708,7 +1760,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1725,7 +1777,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="30">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1742,7 +1794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1759,7 +1811,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="60">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1776,7 +1828,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="60">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1793,7 +1845,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1810,7 +1862,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="60">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1827,7 +1879,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1844,7 +1896,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1861,7 +1913,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="30">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1878,7 +1930,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="30">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1895,7 +1947,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1912,7 +1964,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1929,7 +1981,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="30">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1946,7 +1998,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="30">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1963,7 +2015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="30">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1980,7 +2032,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1997,7 +2049,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2014,7 +2066,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2031,7 +2083,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2048,7 +2100,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2065,7 +2117,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="45">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2082,7 +2134,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="30">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2099,7 +2151,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="30">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2116,7 +2168,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="30">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2133,7 +2185,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2150,7 +2202,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="45">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2167,7 +2219,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2184,7 +2236,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2201,7 +2253,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2218,7 +2270,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2235,7 +2287,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2252,7 +2304,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2269,7 +2321,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2286,7 +2338,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2303,7 +2355,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="30">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2320,7 +2372,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="45">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2337,7 +2389,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="45">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2354,7 +2406,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="30">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2371,7 +2423,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2388,7 +2440,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="45">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2405,7 +2457,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="30">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2422,7 +2474,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="45">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2448,16 +2500,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C86412D-EF50-4A2E-8A10-147D1E09B5C3}">
   <dimension ref="A1:F121"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -2474,7 +2526,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2491,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2505,7 +2557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2516,7 +2568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2527,7 +2579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2538,7 +2590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2552,7 +2604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>3</v>
       </c>
@@ -2563,7 +2615,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2577,7 +2629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>3</v>
       </c>
@@ -2591,7 +2643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>3</v>
       </c>
@@ -2605,7 +2657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>3</v>
       </c>
@@ -2619,7 +2671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>4</v>
       </c>
@@ -2633,7 +2685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>4</v>
       </c>
@@ -2650,7 +2702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>4</v>
       </c>
@@ -2664,7 +2716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>4</v>
       </c>
@@ -2675,7 +2727,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2686,7 +2738,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>5</v>
       </c>
@@ -2697,7 +2749,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2711,7 +2763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2723,7 +2775,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>7</v>
       </c>
@@ -2737,7 +2789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>7</v>
       </c>
@@ -2751,7 +2803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>7</v>
       </c>
@@ -2762,7 +2814,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>7</v>
       </c>
@@ -2773,7 +2825,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>7</v>
       </c>
@@ -2787,7 +2839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>7</v>
       </c>
@@ -2798,7 +2850,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>8</v>
       </c>
@@ -2812,7 +2864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>8</v>
       </c>
@@ -2826,7 +2878,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>8</v>
       </c>
@@ -2837,7 +2889,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>10</v>
       </c>
@@ -2848,7 +2900,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>10</v>
       </c>
@@ -2862,7 +2914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>11</v>
       </c>
@@ -2876,7 +2928,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>11</v>
       </c>
@@ -2890,7 +2942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>12</v>
       </c>
@@ -2904,7 +2956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>12</v>
       </c>
@@ -2918,7 +2970,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>12</v>
       </c>
@@ -2932,7 +2984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>13</v>
       </c>
@@ -2946,7 +2998,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>13</v>
       </c>
@@ -2960,7 +3012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>13</v>
       </c>
@@ -2974,7 +3026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>14</v>
       </c>
@@ -2985,7 +3037,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>14</v>
       </c>
@@ -2999,7 +3051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3013,7 +3065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3024,7 +3076,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>14</v>
       </c>
@@ -3041,7 +3093,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>14</v>
       </c>
@@ -3055,7 +3107,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>15</v>
       </c>
@@ -3069,7 +3121,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>15</v>
       </c>
@@ -3083,7 +3135,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>15</v>
       </c>
@@ -3097,7 +3149,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>15</v>
       </c>
@@ -3108,7 +3160,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>15</v>
       </c>
@@ -3119,7 +3171,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>15</v>
       </c>
@@ -3136,7 +3188,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>15</v>
       </c>
@@ -3150,7 +3202,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>15</v>
       </c>
@@ -3161,7 +3213,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>15</v>
       </c>
@@ -3175,7 +3227,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>16</v>
       </c>
@@ -3186,7 +3238,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>16</v>
       </c>
@@ -3200,7 +3252,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>16</v>
       </c>
@@ -3214,7 +3266,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>16</v>
       </c>
@@ -3231,7 +3283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>16</v>
       </c>
@@ -3248,7 +3300,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>17</v>
       </c>
@@ -3262,7 +3314,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>17</v>
       </c>
@@ -3282,7 +3334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>17</v>
       </c>
@@ -3302,7 +3354,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>17</v>
       </c>
@@ -3316,7 +3368,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>17</v>
       </c>
@@ -3330,7 +3382,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>17</v>
       </c>
@@ -3344,7 +3396,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>17</v>
       </c>
@@ -3361,7 +3413,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>18</v>
       </c>
@@ -3375,7 +3427,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>18</v>
       </c>
@@ -3389,7 +3441,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>18</v>
       </c>
@@ -3403,7 +3455,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>20</v>
       </c>
@@ -3417,7 +3469,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>21</v>
       </c>
@@ -3431,7 +3483,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>21</v>
       </c>
@@ -3445,7 +3497,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>23</v>
       </c>
@@ -3459,7 +3511,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>23</v>
       </c>
@@ -3473,7 +3525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>23</v>
       </c>
@@ -3487,7 +3539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>23</v>
       </c>
@@ -3498,7 +3550,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>23</v>
       </c>
@@ -3512,7 +3564,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>23</v>
       </c>
@@ -3523,7 +3575,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>23</v>
       </c>
@@ -3540,7 +3592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>24</v>
       </c>
@@ -3557,7 +3609,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>24</v>
       </c>
@@ -3571,7 +3623,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>24</v>
       </c>
@@ -3585,7 +3637,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83">
         <v>24</v>
       </c>
@@ -3599,7 +3651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84">
         <v>25</v>
       </c>
@@ -3616,7 +3668,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85">
         <v>25</v>
       </c>
@@ -3630,7 +3682,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86">
         <v>26</v>
       </c>
@@ -3644,7 +3696,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87">
         <v>26</v>
       </c>
@@ -3661,7 +3713,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88">
         <v>29</v>
       </c>
@@ -3675,7 +3727,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89">
         <v>30</v>
       </c>
@@ -3692,7 +3744,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90">
         <v>32</v>
       </c>
@@ -3706,7 +3758,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91">
         <v>32</v>
       </c>
@@ -3720,7 +3772,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92">
         <v>33</v>
       </c>
@@ -3734,7 +3786,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93">
         <v>34</v>
       </c>
@@ -3748,7 +3800,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94">
         <v>34</v>
       </c>
@@ -3762,7 +3814,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95">
         <v>34</v>
       </c>
@@ -3776,7 +3828,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96">
         <v>34</v>
       </c>
@@ -3790,7 +3842,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97">
         <v>34</v>
       </c>
@@ -3804,7 +3856,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98">
         <v>35</v>
       </c>
@@ -3824,7 +3876,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99">
         <v>37</v>
       </c>
@@ -3841,7 +3893,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100">
         <v>38</v>
       </c>
@@ -3855,7 +3907,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101">
         <v>38</v>
       </c>
@@ -3869,7 +3921,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102">
         <v>39</v>
       </c>
@@ -3886,7 +3938,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103">
         <v>39</v>
       </c>
@@ -3900,7 +3952,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104">
         <v>40</v>
       </c>
@@ -3914,7 +3966,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105">
         <v>41</v>
       </c>
@@ -3928,7 +3980,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106">
         <v>46</v>
       </c>
@@ -3942,7 +3994,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107">
         <v>47</v>
       </c>
@@ -3956,7 +4008,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108">
         <v>47</v>
       </c>
@@ -3976,7 +4028,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109">
         <v>48</v>
       </c>
@@ -3990,7 +4042,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110">
         <v>48</v>
       </c>
@@ -4004,7 +4056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111">
         <v>48</v>
       </c>
@@ -4018,7 +4070,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112">
         <v>48</v>
       </c>
@@ -4032,7 +4084,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113">
         <v>51</v>
       </c>
@@ -4046,7 +4098,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114">
         <v>51</v>
       </c>
@@ -4060,7 +4112,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115">
         <v>51</v>
       </c>
@@ -4074,7 +4126,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116">
         <v>52</v>
       </c>
@@ -4088,7 +4140,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117">
         <v>52</v>
       </c>
@@ -4102,7 +4154,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118">
         <v>52</v>
       </c>
@@ -4116,7 +4168,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119">
         <v>53</v>
       </c>
@@ -4130,7 +4182,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120">
         <v>53</v>
       </c>
@@ -4144,7 +4196,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121">
         <v>53</v>
       </c>
@@ -4168,15 +4220,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB71F98-C214-4E2A-8F31-34FC50527B4A}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="82.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4193,7 +4245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4219,15 +4271,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F015AC71-3C0E-4B3C-9B3E-599310938E5F}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4244,7 +4296,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4255,7 +4307,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4266,16 +4318,16 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5">
       <c r="B20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5">
       <c r="B26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5">
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
     </row>
@@ -4283,4 +4335,219 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D110399E-BAEF-427B-901B-08A412CD568E}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6" style="7" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="7" bestFit="1"/>
+    <col min="3" max="3" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="82.42578125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{167A49E4-7B2B-4313-A885-3BE42FE0FB18}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/docs/datas/articles.xlsx
+++ b/public/docs/datas/articles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A558F5-3564-4380-B530-00AA1EAD4A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584B8650-97C4-4895-9F1F-20DC3CBE1E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32955" yWindow="-1395" windowWidth="28800" windowHeight="15885" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30420" yWindow="-1005" windowWidth="20115" windowHeight="15885" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_contents" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="03_contents" sheetId="5" r:id="rId5"/>
     <sheet name="03_words" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="364">
   <si>
     <t>type</t>
   </si>
@@ -1207,6 +1207,126 @@
   </si>
   <si>
     <t>充满活力 迈向未来</t>
+  </si>
+  <si>
+    <t>Software-defined vehicle (SDV) is driving the transformation: It will enable to improve time to market, cost reduction, and innovation simultaneously</t>
+  </si>
+  <si>
+    <t>软件定义汽车 (SDV) 正在推动变革：它将同时缩短产品上市时间、降低成本并促进创新。</t>
+  </si>
+  <si>
+    <t>UX INNOVATION</t>
+  </si>
+  <si>
+    <t>用户体验创新</t>
+  </si>
+  <si>
+    <t>Differentation and user experience (UX) through continuous software feature updates;</t>
+  </si>
+  <si>
+    <t>通过持续的软件功能更新实现差异化和提升用户体验；</t>
+  </si>
+  <si>
+    <t>Value for money: enhanced features, optimized costs;</t>
+  </si>
+  <si>
+    <t>性价比高：功能增强，成本优化；</t>
+  </si>
+  <si>
+    <t>Personalization and new software features through cross domain integration of software.</t>
+  </si>
+  <si>
+    <t>通过跨领域软件集成实现个性化和新的软件功能。</t>
+  </si>
+  <si>
+    <t>COST REDUCTION</t>
+  </si>
+  <si>
+    <t>降低成本</t>
+  </si>
+  <si>
+    <t>Requirements derived top down from user needs and central intelligence unit;</t>
+  </si>
+  <si>
+    <t>需求自上而下地从用户需求和中央情报部门提出；</t>
+  </si>
+  <si>
+    <t>“Good enough” specifications;</t>
+  </si>
+  <si>
+    <t>“足够好”的规格；</t>
+  </si>
+  <si>
+    <t>SPEED AND TIME-TO-MARKET (TTM)</t>
+  </si>
+  <si>
+    <t>速度和上市时间 (TTM)</t>
+  </si>
+  <si>
+    <t>Daily updates and continuous feature deployment;</t>
+  </si>
+  <si>
+    <t>每日更新和持续功能部署；</t>
+  </si>
+  <si>
+    <t>Virtualization and end-to-end development pipeline;</t>
+  </si>
+  <si>
+    <t>虚拟化和端到端开发流程；</t>
+  </si>
+  <si>
+    <t>Reusable software and functional stacks for new platforms.</t>
+  </si>
+  <si>
+    <t>Standardized hardware and interfaces across all vehicle systems and components driven and enabled by decoupling from software and hardware.</t>
+  </si>
+  <si>
+    <t>适用于新平台的可重用软件和功能栈。</t>
+  </si>
+  <si>
+    <t>通过软件和硬件的解耦，实现车辆所有系统和组件的标准化硬件和接口。</t>
+  </si>
+  <si>
+    <t>Software-defined vehicle evolves throughout its life cycle: It changes its key features by changing software onboard and offboard and drives hardware towards standardization, simplification, integration, and cost reduction.</t>
+  </si>
+  <si>
+    <t>软件定义汽车在其整个生命周期中不断发展：它通过改变车载和车外的软件来改变其关键特性，并推动硬件朝着标准化、简化、集成和降低成本的方向发展。</t>
+  </si>
+  <si>
+    <t>Our path is clearly visible ahead of us</t>
+  </si>
+  <si>
+    <t>我们前方的道路清晰可见</t>
+  </si>
+  <si>
+    <t>BM's global team is firmly committed to offering technology and services “Invented for life” that make mobility safer, more sustainable, and exciting.</t>
+  </si>
+  <si>
+    <t>BM 的全球团队坚定致力于提供“为生活而发明”的技术和服务，使出行更安全、更可持续、更令人兴奋。</t>
+  </si>
+  <si>
+    <t>To create added value for customers BBM offers integrated mobility solutions and services along the tech stack.</t>
+  </si>
+  <si>
+    <t>为了给客户创造附加值，BBM 提供基于技术栈的集成移动解决方案和服务。</t>
+  </si>
+  <si>
+    <t>By setting clear goals for 2030, we are well on our way to shaping a new era of mobility.</t>
+  </si>
+  <si>
+    <t>Together.</t>
+  </si>
+  <si>
+    <t>通过设定明确的2030年目标，我们正朝着塑造出行新时代稳步迈进。</t>
+  </si>
+  <si>
+    <t>携手共进。</t>
+  </si>
+  <si>
+    <t>By 2030, we are the preferred partner for vehicle systems, software and hardware and the world‘s leading technology provider for mobility life cycle businesses.</t>
+  </si>
+  <si>
+    <t>到 2030 年，我们将成为车辆系统、软件和硬件的首选合作伙伴，以及全球领先的移动出行生命周期业务技术提供商。</t>
   </si>
 </sst>
 </file>
@@ -4339,7 +4459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D110399E-BAEF-427B-901B-08A412CD568E}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" style="7" customWidth="1"/>
@@ -4499,6 +4619,346 @@
       </c>
       <c r="E9" s="7" t="s">
         <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="7">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7">
+        <v>5</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7">
+        <v>6</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7">
+        <v>6</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7">
+        <v>6</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7">
+        <v>7</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7">
+        <v>8</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="7">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7">
+        <v>8</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7">
+        <v>9</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="7">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="7">
+        <v>11</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="7">
+        <v>11</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="7">
+        <v>11</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7">
+        <v>11</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7">
+        <v>11</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
